--- a/results/SPs_GSE13355_13_5_5.xlsx
+++ b/results/SPs_GSE13355_13_5_5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="78">
   <si>
     <t>classifier</t>
   </si>
@@ -70,54 +70,54 @@
     <t>log_loss</t>
   </si>
   <si>
+    <t>BAGGNG</t>
+  </si>
+  <si>
+    <t>POM_ENTROPY</t>
+  </si>
+  <si>
     <t>POM_enGROUPS</t>
   </si>
   <si>
     <t>RND_FST</t>
   </si>
   <si>
-    <t>POM_ENTROPY</t>
-  </si>
-  <si>
     <t>POM_ALG</t>
   </si>
   <si>
     <t>SVC</t>
   </si>
   <si>
-    <t>BAGGNG</t>
-  </si>
-  <si>
     <t>MLP</t>
   </si>
   <si>
+    <t>3NN_MUL</t>
+  </si>
+  <si>
+    <t>3NN_OVR</t>
+  </si>
+  <si>
+    <t>7NN_MUL</t>
+  </si>
+  <si>
+    <t>7NN_OVR</t>
+  </si>
+  <si>
+    <t>5NN_MUL</t>
+  </si>
+  <si>
     <t>5NN_OVR</t>
   </si>
   <si>
-    <t>5NN_MUL</t>
-  </si>
-  <si>
-    <t>7NN_OVR</t>
-  </si>
-  <si>
-    <t>7NN_MUL</t>
-  </si>
-  <si>
-    <t>3NN_MUL</t>
-  </si>
-  <si>
-    <t>3NN_OVR</t>
-  </si>
-  <si>
     <t>7NN_OVO</t>
   </si>
   <si>
+    <t>3NN_OVO</t>
+  </si>
+  <si>
     <t>5NN_OVO</t>
   </si>
   <si>
-    <t>3NN_OVO</t>
-  </si>
-  <si>
     <t>DEC_TRE</t>
   </si>
   <si>
@@ -130,136 +130,112 @@
     <t>1NN_OVO</t>
   </si>
   <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
     <t>A4</t>
   </si>
   <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>A2</t>
+    <t>A9</t>
   </si>
   <si>
     <t>A3</t>
   </si>
   <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
     <t>A6</t>
   </si>
   <si>
-    <t>A8</t>
-  </si>
-  <si>
     <t>xuyager</t>
   </si>
   <si>
+    <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.8353617820796139, 0.4828227322648379, 0.8794134754299001, 0.5219619130429735, 0.5186625208506368, 0.8820289019076218, 0.5147574573379397, 0.4611078477666036, 0.5154320529018704, 0.8635365202045711, 0.48676038891709783, 0.898683553773353, 0.5139611868945718, 0.4651084615520684, 0.9241635681812777, 0.9052995940365394, 0.8564337605789073, 0.8908711059784495, 0.9121506167529719, 0.47647800555890485], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.4448098078169497, 0.4602971144752979, 0.44807070945261757, 0.4733840472119207, 0.45977554064239545, 0.4560794390367049, 0.47332670349884476, 0.4424244628954341, 0.4668295254611146, 0.4202209173465909, 0.44257572921058413, 0.47682027937362115, 0.4896603288585829, 0.4451457810467952, 0.46598951491132895, 0.4673528819069166, 0.45546250290237394, 0.4392480490136758, 0.44831416357741644, 0.4840858497409366], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.43693895773917635, 0.46809275719918897, 0.452760900715789, 0.4562855377478568, 0.44041088707344495, 0.4557033573892624, 0.47311139789178, 0.44281939792908515, 0.4608280629035107, 0.42374627220634664, 0.453711322890823, 0.4718265917194709, 0.4755784187186918, 0.43952004430637504, 0.46073632300532685, 0.45897644157132017, 0.4457188428887905, 0.45641431689929696, 0.463113171987358, 0.467402274714688], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [3.872603307547613, 2.9835073256781106, 0.5003757075069356, 3.321817480342171, 6.637715661267636, 0.780063583407504, 9.232886434805533, 0.6462026763069569, 10.958233569233188, 0.5937746447391711, 0.8560643880202131, 0.7680580225338924, 9.010670737516598, 0.639366108198946, 1.271678814010188, 7.502879209986353, 0.8590587694260337, 2.032754074222848, 3.297105340315569, 6.61308303202235], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.5323398323403775, 0.5816553236375993, 2.2530377938702446, 0.4783453024813694, 0.46329832299946694, 1.2946759779193546, 2.5857794480128717, 0.5023604976842674, 0.670616565529324, 0.33006921560551694, 5.588081256045546, 0.6162186765481596, 0.6647609733699403, 0.60163257883982, 0.6060350117105103, 0.525576442976155, 0.4444454846747913, 0.5446154921694895, 0.5895523915748746, 0.5728814857310313], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.5808700960532241, 0.6730308269017884, 0.3994577093303866, 0.6347790073381262, 0.42779758022902914, 0.45382195673652465, 0.5951947464060791, 0.5021431497048829, 0.7221021982418614, 0.3396325925689876, 0.6405868458965019, 0.5906107671271521, 0.7983152254880688, 2.8707323318695073, 3.2564561378288532, 0.4789149745690643, 0.5214056592144963, 0.438166879227154, 0.5199445052991751, 0.6750718296318206], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.5469539666832948, 0.5650147784622814, 0.4956396109375141, 0.5415988588251338, 0.4774248353260239, 0.5469069627289954, 0.582088608051369, 0.5644284806881975, 0.5654308630741304, 0.453522231684812, 0.5191399201969022, 0.5257960192730178, 0.5470074294997319, 0.46856080575340553, 0.5117002412190603, 0.5109834998196058, 0.5653221083941462, 0.5318003031389684, 0.5531672357309017, 0.5754961887293365], \'SVC(C=1, random_state=13)\': [0.5752203853880767, 0.5561478572599988, 0.5493209082821467, 0.5658104853172694, 0.5386681669882443, 0.5400406859476976, 0.5701923508289755, 0.5820178449221477, 0.5583435328785353, 0.4951362345509244, 0.5293406089399951, 0.5798469731042455, 0.5949028085377802, 0.5403303708925076, 0.5509166984915542, 0.5410260469248327, 0.5517873547796363, 0.5400257534166675, 0.5442036238688869, 0.554296642923225], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.534254234771837, 0.5273872408839632, 0.48324870300022216, 0.5408277170907883, 0.4776672821186642, 0.5339482348660229, 0.5563932253073968, 0.5642858509064503, 0.5522514349208141, 0.4670997505657969, 0.504763735500974, 0.5009815493105495, 0.5580931489728133, 0.48158416985942454, 0.5114098646136128, 0.5598425599674474, 0.5399920066533174, 0.5323396001061841, 0.5533169890115125, 0.5749887413669309], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.344650878660001, 9.789634253834288, 10.234617629008575, 9.789634253834288, 10.234617629008575, 9.344650878660001, 9.789634253834288, 10.234617629008573, 11.569567754531432, 9.789634253834288, 9.344650878660001, 9.789634253834288, 8.454684128311431, 11.124584379357145, 9.344650878660001, 9.789634253834288, 11.124584379357145, 11.124584379357145, 10.234617629008575, 10.234617629008575], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [3.8312965916009603, 1.2757177041598182, 1.3063955640337443, 1.742010862478681, 1.7242527098582006, 3.4113419268037224, 1.7242527098582003, 4.726269084024941, 3.008502007205494, 2.162776231405763, 2.1241844063538013, 2.1627762314057635, 2.5906448613810387, 1.7449190855813075, 3.03917986707942, 4.733372345073134, 2.998490523054675, 1.7192469677827908, 0.911302312905178, 2.952795436954521], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.7661734745942168, 0.4656262819843586, 0.8797206186686329, 0.9203521485217185, 0.4360379906012338, 1.3088461138430836, 0.4570110952131942, 1.3499676866732122, 0.9226608461105871, 0.8325275391094544, 0.8579068602830657, 0.9558007680178079, 0.9605953314771317, 0.462674176974021, 0.48252984856728404, 2.1901837451565425, 1.7914572454950608, 0.8564388164678043, 0.9299035393392576, 1.704218229332607]}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.5533409945100276, 0.49653406842263353, 0.45470016392746565, 0.5357250962620629, 0.5308675756695341, 0.5318662354265854, 0.9517284948693846, 0.5720059029556479, 0.49164859622955975, 0.8881190695122864, 0.5104529368556585, 1.3433106737670002, 0.8678877447866, 0.9150975788017638, 0.951361129616835, 0.44001961623385333, 0.49849779959901164, 1.3899643627535883, 0.9230549244649827, 0.5248538831121432], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.48013963802406173, 0.503913136154145, 0.4513851933773866, 0.46084079486297347, 0.48712449829804627, 0.4645055118244897, 0.4964247615423023, 0.4902817463683743, 0.46304834311624116, 0.4745804243077629, 0.5006032947972805, 0.4763404082564848, 0.44349523777411864, 0.510240993900472, 0.4857745840747887, 0.45989068842499714, 0.49071206759612823, 0.47640790458648363, 0.45283984485976897, 0.46684056598825574], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.4709196454143003, 0.49494272823473234, 0.44559228297595715, 0.46321950928953654, 0.46499781940823093, 0.46324216625490866, 0.4989417506763165, 0.4821206352769668, 0.4616573820927635, 0.4780748416409049, 0.506726783781038, 0.4603529597904755, 0.45462736007908117, 0.5093395240393098, 0.4799760308237565, 0.45488735230478017, 0.4768437498101793, 0.4684608513480061, 0.45216916988036343, 0.45839344445623165], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [4.407392947257534, 7.180033651362842, 0.3512491867661633, 12.116053418974184, 0.47639512521046523, 5.956986061896057, 8.996938051687584, 6.642817543848968, 1.2942481588955865, 5.004704269077905, 0.9433947772382058, 1.3505536984458024, 1.1441897596056405, 1.4177993988052646, 7.684397047305952, 0.7206087652726014, 0.48765854242111345, 1.3364402607651322, 1.1693119951722357, 2.616928193129867], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4418850256493078, 0.5296828541817209, 0.8429988297935617, 0.4876313093039208, 0.43108395804677196, 0.4459548998896092, 0.7510591242995454, 0.533350544751543, 0.48446944993259766, 0.3837297237464982, 0.6227416610501949, 1.4501496665321356, 1.5805025113678908, 1.7899040249848734, 0.5017687051064457, 0.4466809910046243, 0.4351146718552623, 0.5835186773396576, 2.3638618245645153, 3.250098048590546], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.2523062045172548, 0.7948681047022833, 1.5109290617875089, 1.3772111529124917, 0.6396551168706854, 0.49986585583345244, 0.9547117482470198, 0.567644306642206, 4.671594497884774, 0.804765291640979, 3.5527964693462217, 0.37316326567387254, 0.9203998792118687, 0.8467659543354604, 4.646603554607988, 0.5435136265077525, 0.556583564157907, 1.3385727487559325, 0.6866200379453956, 0.3879051223489701], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.5628558907047433, 0.554181204586666, 0.5125097403222919, 0.5370070420047256, 0.509874125380322, 0.5169519828652325, 0.6098272689379775, 0.5679661855929746, 0.5116088287905614, 0.4839637656110109, 0.6002613304238374, 0.4799125732587339, 0.48526442568094563, 0.6273180486834572, 0.5400361691609362, 0.5464563340982266, 0.5856299086226011, 0.5337543664919878, 0.5670632101513736, 0.481073549693949], \'SVC(C=1, random_state=13)\': [0.6064079829117369, 0.6068449686082268, 0.5620335990938478, 0.5723411321771731, 0.5675601994905389, 0.5764219322209259, 0.6347368833640978, 0.6042143059620187, 0.5794223495208162, 0.5005797153356378, 0.6344542123069898, 0.5409776612425485, 0.45074335134021826, 0.6972368633539212, 0.5806111134636253, 0.5870266574929536, 0.6040475039393194, 0.596020872795128, 0.5884208441302977, 0.5117577731210439], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.5380928350028026, 0.5284297259070256, 0.5128725371051933, 0.5494438582518277, 0.4982013393721465, 0.5169264273867945, 0.6095109940377715, 0.5675292707081131, 0.5373420383162983, 0.47233280311905673, 0.6005146432211916, 0.4691301992060559, 0.49761152273374526, 0.6277619441874285, 0.5397736696026852, 0.5463877969831613, 0.5863380950113106, 0.5462655386670913, 0.5796082861258771, 0.46957807851856675], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [12.459534504880002, 10.234617629008575, 9.344650878660001, 8.009700753137144, 11.124584379357145, 12.90451788005429, 9.789634253834288, 12.014551129705717, 10.67960100418286, 10.234617629008575, 12.014551129705717, 12.014551129705717, 12.459534504880002, 11.569567754531432, 11.569567754531432, 9.344650878660003, 11.569567754531432, 9.789634253834288, 12.014551129705717, 10.679601004182858], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.199913944906412, 2.154218858806258, 2.653454692680204, 2.593553084483665, 2.6142194602067717, 5.256182777772812, 1.267160331560313, 2.6306907979843137, 3.465594385503382, 3.0748634690287555, 0.5063648743341679, 2.5806333772302192, 2.219126209078206, 2.203465575430508, 2.5856391193056285, 4.305503715097858, 2.1978164259336292, 2.6163169791795546, 2.609857125552832, 1.2913783378075159], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.360387595792254, 1.829085001972752, 0.5686653639749888, 0.9460681482279463, 0.4389462137038606, 1.4178410742194456, 0.8850191573689474, 0.9122032008904364, 1.347059463570585, 0.9559402001982865, 0.475777198315656, 0.901183766257636, 0.5132077084412099, 0.936223960785502, 1.7828998728955552, 1.7457043452232475, 0.48773283699483094, 1.7357506752440874, 0.8914650787317222, 0.901490495146489]}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.9494481632309408, 0.8572953089249886, 1.383446694955207, 0.5856622471338215, 0.4908957062713748, 0.9884061150367532, 0.5088976306475035, 0.518649412735508, 0.4425389910162792, 0.4780119157720571, 0.9348734517331877, 0.8922670806318127, 0.9438233189937508, 0.9367197352192677, 0.9030319561633448, 0.5726493103771172, 0.5179692644110915, 0.5580371855045468, 0.5279350473072189, 0.5593546870674188], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.5373207139999512, 0.455466590836293, 0.4900931025996767, 0.48959217027054097, 0.4493145687837656, 0.49266026298907045, 0.4708298864770928, 0.48056344986281163, 0.4709521424716273, 0.4712054476760367, 0.4597291519332339, 0.4767359556039375, 0.5094730216188721, 0.4714101057735012, 0.48984777192009704, 0.481574660066949, 0.4827645369295002, 0.48029728262417015, 0.5142647618252185, 0.5114091149590138], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.5451855071888845, 0.46060131880324023, 0.4977454861651916, 0.48516239216782736, 0.45101634165798277, 0.4803493145543935, 0.46516455630423914, 0.46631231892491315, 0.4715967136055002, 0.4526907587582727, 0.4656051989973276, 0.4873490584529514, 0.4980010957321722, 0.463832888828161, 0.4851986393909828, 0.47727227981209064, 0.4912423928204469, 0.48004832516972656, 0.5168998382269271, 0.5136380372956091], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [8.978823775282667, 4.588677967634678, 2.081548398435936, 2.115001700456233, 1.1781110266135995, 1.8662633563507949, 0.7889986644455501, 7.289659717141647, 1.1263333102724644, 1.2621304196860936, 9.000501274412901, 0.6233939041535903, 1.3801908884339678, 5.941246169851155, 4.9469552186113255, 7.43768200842868, 6.057541370798982, 1.0513988895698134, 1.5240462179213088, 2.3899697179833055], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.1614387896581313, 0.5027904779202558, 1.4833120253989072, 4.771759602897912, 1.1166636113898032, 1.9079908320704277, 0.49879293548652076, 0.5156809433364639, 1.3118085626567233, 0.5416901243851227, 0.5036567702086491, 0.4741757303581516, 0.5693285791680904, 3.025795511915403, 0.4857218442967036, 0.6198675022219043, 0.622774989986855, 3.1962492586330353, 1.5272351269432662, 0.4920864035740337], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.3676251559222454, 3.828902983710721, 0.8452520608510513, 0.5100865451220427, 1.316210464402765, 2.42675913546479, 0.5461288698283182, 0.5475803054770156, 0.3917105435487769, 0.5456416337882283, 0.6509356505329926, 0.6250249692465649, 0.6052395418162999, 0.6899105194698059, 0.6270479949425734, 0.6131848349758374, 0.7246611879083654, 0.48994206534369944, 0.7827097606246359, 4.1369163206895285], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.6399647288146679, 0.5782429161154176, 0.6251615856005155, 0.5672203096442244, 0.59319793290277, 0.5922681891865984, 0.5355186644807866, 0.5824789449010334, 0.5118233676594931, 0.5574342545105626, 0.5683840981802187, 0.5523573224330613, 0.5782803760841077, 0.5657926767844516, 0.5527764754944096, 0.6078923803199311, 0.607363187901965, 0.5158362316283587, 0.615886911044477, 0.5565690697715381], \'SVC(C=1, random_state=13)\': [0.6550649561112943, 0.5926943940303537, 0.598847262267915, 0.6192911318112388, 0.6449324637371977, 0.5849695432459574, 0.593637576500804, 0.6072015758081701, 0.5925925304322334, 0.5948600842027166, 0.6357012235934926, 0.5941953489890297, 0.6207539629327145, 0.5671102924700981, 0.5957768728044402, 0.6434779521009067, 0.5958454302492323, 0.5670769770107261, 0.637278559787778, 0.5950866918225086], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.6395775043358317, 0.5769640272692695, 0.6123433624283181, 0.5922088197028811, 0.6051556127773902, 0.5801858100992793, 0.523230375712659, 0.596971628829164, 0.5230700330658079, 0.558430102271099, 0.5679207654275158, 0.5644734609173067, 0.5778074522109876, 0.5535149834554014, 0.5650889967485818, 0.6209698961542588, 0.6071532233627288, 0.5025129276975221, 0.6039912507211842, 0.5440724570895589], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [11.56956775453143, 10.679601004182858, 12.459534504880002, 12.90451788005429, 9.789634253834288, 11.569567754531432, 11.569567754531432, 10.234617629008575, 12.459534504880002, 8.454684128311431, 12.014551129705717, 11.569567754531432, 10.234617629008575, 11.124584379357145, 11.124584379357145, 13.349501255228576, 8.899667503485716, 11.569567754531432, 11.124584379357145, 11.56956775453143], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [4.779878135303132, 5.582649751396961, 4.783429765827228, 3.9155835027530768, 2.6063054950287357, 5.616879241794981, 3.904117907050944, 1.7835109106332696, 2.5998456414020126, 1.7599363118075355, 2.203465575430508, 1.3170504556060325, 1.692120738432961, 1.7278043403822965, 4.314871791827208, 3.528404216802547, 1.2857291883106372, 4.340543909625725, 2.993484780979266, 2.6327883169570963], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.4123891710747045, 3.893700417971895, 0.9318616261315619, 0.9428371788566513, 0.897128160492549, 4.3753035991418905, 0.9150536098214042, 0.9399867699256838, 1.3075314344722488, 0.9265770196951955, 1.3855557383497799, 0.4890335841017177, 0.8609983974738817, 0.44119709712106986, 3.4993223207004047, 1.0236024091284346, 0.48013953296959616, 1.3797532244084745, 1.7596320029586747, 0.5061622615646767]}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.3297313060586287, 0.5022051153370433, 0.5272720632377274, 0.502687193160503, 1.4302103679010383, 0.885873329056623, 0.531431685851693, 0.8806246393743845, 0.5757085771546618, 0.5028462019890038, 0.9548391072856945, 0.5014414380332383, 0.45563404720433137, 0.478414194933678, 0.47967388232489083, 0.8859745237134649, 0.5443896306287753, 0.5088593931238666, 0.4954357106294302, 0.5302125567536257], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.46663619712049415, 0.5032725016096049, 0.48701547014653496, 0.46789595926263855, 0.5504616497508685, 0.4643369031540448, 0.5025974334744973, 0.459453490051502, 0.5148023286300796, 0.463289755718362, 0.5113617046761596, 0.450604901748846, 0.4575644028373959, 0.44634328212223173, 0.4674912876860247, 0.46262784837803445, 0.49556247034091533, 0.4589771193439382, 0.4672363006929017, 0.4894236974976183], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.4627953756278185, 0.4803467541065393, 0.4794962220511172, 0.46898771062733824, 0.5386956374556899, 0.47142880508304796, 0.4917270328792927, 0.46412834752964727, 0.5019093448907997, 0.45315275740133854, 0.497136158056559, 0.45155225099596885, 0.46036025126466984, 0.449697351607175, 0.4822374892060741, 0.4548190695908191, 0.48402927816023966, 0.46760004584436815, 0.47281510156211237, 0.4694201719506286], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [5.76147719901364, 0.8123262651120949, 1.933644385289468, 8.69643787726678, 1.3623190523274604, 5.090991245860325, 5.864610602792022, 0.6263381152717236, 3.4924626031441237, 4.870500020225078, 1.3517006293262552, 6.624380291242471, 5.5668746179361, 1.0044398212995589, 5.497262671210194, 0.6041755215807264, 5.9991360306708446, 7.582934486031496, 3.0332510889977393, 7.41611896173856], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4825893710925593, 2.0442608185769817, 0.6689131478117806, 0.7819248355706457, 0.7819253650512885, 0.7935493220141632, 3.03814403849175, 0.4613449544362245, 0.6539397488121563, 0.5149941661413453, 1.8911472403663827, 0.3917666862453332, 3.0805441445722064, 0.46397195094699567, 0.4849315315980276, 0.4398736961016312, 0.6796529441445668, 2.183176733292357, 2.0279578820636184, 0.6090794073978922], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.4944218306361311, 0.5715782987789221, 0.6829127239091277, 0.5780393032115052, 0.6975820132263193, 0.48946090277730037, 0.5395112902549135, 0.8998934949601997, 0.7677742107552115, 0.39918651691412776, 1.1585381346302228, 0.3914519184275907, 5.104046990345675, 0.4782464963473856, 0.5141745520994787, 0.5134886460967567, 2.7356061514133847, 0.6262688350361058, 0.413233286989172, 0.6428862964612134], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.49211263339819433, 0.567625010440826, 0.5906543100540211, 0.592498655938098, 0.6498069661558469, 0.5833626728030742, 0.5292134392902005, 0.5140976710124259, 0.6242111458512125, 0.5248656384661574, 0.5744858496883876, 0.5166221497208863, 0.5270219174791353, 0.49997626086508856, 0.5634852969039692, 0.49575876681248515, 0.5567570735231421, 0.5676262481032375, 0.5519964298999406, 0.5505169242098833], \'SVC(C=1, random_state=13)\': [0.5377668033299814, 0.6373007365406143, 0.6060727497473606, 0.5554220006558742, 0.6676190073223972, 0.6192798481440541, 0.6091332576436209, 0.5541122303654918, 0.6232017817552727, 0.5351166414816364, 0.647002702371878, 0.5536563917400319, 0.5424363469107829, 0.5542389173669985, 0.5914242749941687, 0.5497879304668113, 0.6099172686393646, 0.6204680525994791, 0.5685028581824249, 0.5520649598346492], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.5045851380903577, 0.5925232250229139, 0.578321013576603, 0.6048666347879419, 0.6628489874104153, 0.5842855916003179, 0.5549858617505111, 0.5144449877357828, 0.5986016958993214, 0.513732017757615, 0.5664877991975071, 0.5157731171271713, 0.5269932470829841, 0.500457716258586, 0.5634173209131458, 0.47113460821487163, 0.5680900286266133, 0.556088446037453, 0.5649043183356104, 0.5257765183267431], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [11.569567754531432, 14.684451380751431, 8.454684128311431, 10.679601004182858, 10.679601004182858, 9.344650878660001, 11.569567754531432, 12.90451788005429, 9.789634253834288, 10.234617629008575, 12.014551129705717, 11.124584379357145, 10.67960100418286, 13.349501255228576, 10.234617629008575, 11.124584379357145, 12.90451788005429, 9.344650878660003, 12.459534504880002, 12.904517880054291], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.657649730625769, 2.1456614862067527, 3.029168382928601, 1.3320676818322608, 2.2406032889311573, 3.4019738500743726, 1.3206020861301286, 2.1842533112587144, 1.7684936844070411, 2.1627762314057635, 1.7392699360844288, 3.8569687093994767, 1.742821566608525, 2.579179265678906, 0.4721353839361458, 1.7278043403822965, 3.051288870203021, 3.5012779874527165, 1.7684936844070411, 2.2120229480300138], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.9207027593182826, 1.3689589006557075, 1.7294441860617915, 0.49855502527549383, 1.0193118209101015, 1.3264886381202456, 0.48963310961547607, 0.9031418530499402, 1.3143857808032464, 0.9120059545382987, 0.9536893167810772, 1.3307554225014184, 0.5109707572879487, 1.2948229058348886, 0.4802789651500747, 1.361630528727482, 0.8924291473059929, 1.8527990329789645, 0.8939410730289654, 0.9155436527984468]}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.48012336700878794, 0.4641988835348916, 0.9080245901236256, 0.5068514573134862, 0.8770120497603012, 0.5468811408833049, 0.4760318444895732, 0.5263681296046245, 0.49995140972779695, 0.8701664927317057, 1.3368616074858977, 0.5288493539360621, 0.44018691294222817, 0.4436453139630654, 0.4653219609376629, 0.5364756654507392, 0.467666073858131, 0.519013131647201, 0.4988013835695369, 0.8861609827199823], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.41412505615259826, 0.43585885296918625, 0.4460543687508004, 0.4640167082649289, 0.4640724129828241, 0.465367707440027, 0.45857178848677266, 0.4761465126707047, 0.47718614991297653, 0.4220114986614098, 0.4534429799589544, 0.5087218128893848, 0.46080733762949344, 0.46646824142151944, 0.44826598762528314, 0.482691872849937, 0.48473422975826497, 0.45091425514965555, 0.5198725171048085, 0.4328250651085418], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.4220865832984423, 0.45398111062572777, 0.45086503032497904, 0.45283311225852463, 0.47788732384657484, 0.4520548126792652, 0.45662279496871677, 0.48176084223305776, 0.47802067941487675, 0.4286164850877819, 0.4634463918459644, 0.49484191524789833, 0.4606153974440306, 0.46625008690631026, 0.44050821780706323, 0.48977840579534143, 0.4812188020905534, 0.44906995957242735, 0.49878081740340025, 0.4450210158610685], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [0.3719127401115828, 0.9271847978607831, 0.7162411334983798, 3.6208688948543535, 7.572015493033243, 2.1828115992649653, 0.9462206336760574, 1.4385168597271014, 0.8396644156259878, 3.6606607757829446, 0.681970354038777, 0.702759905206444, 1.4879336926873092, 1.459416680853379, 0.5655680675691006, 1.789385501310566, 0.6664473481436461, 0.5275397525070169, 1.009582895397952, 5.060519967667833], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.3666203971817525, 0.48246629718033407, 2.9875678583877576, 0.6289014893291228, 0.7753163356716251, 1.9708190671100505, 0.5024680287322868, 0.6693175368851885, 4.823512736601244, 0.9527555295876449, 1.3796346134341542, 3.5251031495260254, 1.6734993344003608, 0.5002741954256522, 2.434512567914482, 0.4452582599888358, 2.963551164541418, 1.7092243977042254, 4.084317396824808, 3.0176732997306472], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.3650951147241029, 0.5060193259510218, 0.5973643612686588, 0.5631057901665083, 3.8157369075624294, 0.5084564183581348, 0.613597970116625, 0.7666170552538538, 0.539397793311692, 0.6578858618672041, 0.6729354705866101, 0.5130856495029913, 0.9373599227568753, 0.46824454565065793, 0.4307464725846885, 0.4121301907954542, 0.48675636024709973, 0.49729236147730044, 0.6445510315562053, 0.5259906625910512], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.4583981660602251, 0.5475594205278997, 0.552560429172596, 0.522607552861004, 0.5866478257060401, 0.5506345984941187, 0.5481992250386192, 0.5614221186138507, 0.5925071758209937, 0.5482312312430627, 0.5329060811062817, 0.6336599401074936, 0.49801529139342404, 0.5260663520803555, 0.4828567036563454, 0.5290841581723115, 0.5423225667484354, 0.4834601917324988, 0.5732574862223778, 0.543898150470975], \'SVC(C=1, random_state=13)\': [0.5008564074508794, 0.5560249540176495, 0.5785417862710076, 0.5542714431128382, 0.5708448716443201, 0.5701077099561149, 0.5669323457135302, 0.6001420283258911, 0.5720293823164454, 0.6064135697209416, 0.5920568925016335, 0.6248053810172451, 0.5662674846826747, 0.5302363740763979, 0.5643412326476306, 0.621258070891408, 0.5911433022584068, 0.5292846895314544, 0.6278156832536066, 0.5918020746038315], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.45877140953414064, 0.5218673115961573, 0.5525748082389775, 0.5113093107324578, 0.5633749854217791, 0.57543232576707, 0.5480659685106958, 0.5615934101551969, 0.5674756594769018, 0.5745326545155169, 0.53489674394039, 0.620681625833759, 0.5178884037022069, 0.5262932662356653, 0.47080102252932415, 0.5289956828729973, 0.5412458016147836, 0.484124128772577, 0.5611106451959147, 0.5324269826497889], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.344650878660001, 10.234617629008575, 10.679601004182858, 10.234617629008575, 13.349501255228576, 10.234617629008575, 10.67960100418286, 12.90451788005429, 12.904517880054291, 11.569567754531434, 6.674750627614288, 11.569567754531432, 9.789634253834288, 9.789634253834288, 9.789634253834288, 10.67960100418286, 11.124584379357145, 11.124584379357145, 12.90451788005429, 9.789634253834288], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [0.8941875677061673, 2.1727877155565825, 2.1763393460806784, 5.569086636722045, 2.2005573523278814, 3.041277386052203, 2.1577704893303538, 2.612121941233989, 2.626328463330374, 2.1949082028310025, 2.1506672282821615, 3.88554905030062, 1.7449190855813075, 2.1542188588062583, 1.2556947358581805, 3.539869812504679, 1.2828209652080105, 2.639891578005289, 4.849791227650489, 5.621241576448923], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.45090185238303543, 1.3440696224591389, 0.4752732230746652, 2.1732223644019584, 1.3396634058974881, 0.542292024583344, 0.5054471077076004, 1.7832504836921195, 0.45359889686957655, 0.9491436680389478, 0.9497870754604169, 0.9275132237415699, 0.8890886953979822, 0.8576001313942123, 0.40821053965827564, 1.41658420902027, 0.8632492808910913, 0.9233181857960044, 0.5737666563231658, 3.1014742109136386]}'}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.8353617820796139, 0.4828227322648379, 0.8794134754299001, 0.5219619130429735, 0.5186625208506368, 0.8820289019076218, 0.5147574573379397, 0.4611078477666036, 0.5154320529018704, 0.8635365202045711, 0.48676038891709783, 0.898683553773353, 0.5139611868945718, 0.4651084615520684, 0.9241635681812777, 0.9052995940365394, 0.8564337605789073, 0.8908711059784495, 0.9121506167529719, 0.47647800555890485], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.4448098078169497, 0.4602971144752979, 0.44807070945261757, 0.4733840472119207, 0.45977554064239545, 0.4560794390367049, 0.47332670349884476, 0.4424244628954341, 0.4668295254611146, 0.4202209173465909, 0.44257572921058413, 0.47682027937362115, 0.4896603288585829, 0.4451457810467952, 0.46598951491132895, 0.4673528819069166, 0.45546250290237394, 0.4392480490136758, 0.44831416357741644, 0.4840858497409366], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.43693895773917635, 0.46809275719918897, 0.452760900715789, 0.4562855377478568, 0.44041088707344495, 0.4557033573892624, 0.47311139789178, 0.44281939792908515, 0.4608280629035107, 0.42374627220634664, 0.453711322890823, 0.4718265917194709, 0.4755784187186918, 0.43952004430637504, 0.46073632300532685, 0.45897644157132017, 0.4457188428887905, 0.45641431689929696, 0.463113171987358, 0.467402274714688], \'MLPClassifier(max_iter=2000, random_state=13)\': [3.872603307547613, 2.9835073256781106, 0.5003757075069356, 3.321817480342171, 6.637715661267636, 0.780063583407504, 9.232886434805533, 0.6462026763069569, 10.958233569233188, 0.5937746447391711, 0.8560643880202131, 0.7680580225338924, 9.010670737516598, 0.639366108198946, 1.271678814010188, 7.502879209986353, 0.8590587694260337, 2.032754074222848, 3.297105340315569, 6.61308303202235], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.5323398323403775, 0.5816553236375993, 2.2530377938702446, 0.4783453024813694, 0.46329832299946694, 1.2946759779193546, 2.5857794480128717, 0.5023604976842674, 0.670616565529324, 0.33006921560551694, 5.588081256045546, 0.6162186765481596, 0.6647609733699403, 0.60163257883982, 0.6060350117105103, 0.525576442976155, 0.4444454846747913, 0.5446154921694895, 0.5895523915748746, 0.5728814857310313], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.5808700960532241, 0.6730308269017884, 0.3994577093303866, 0.6347790073381262, 0.42779758022902914, 0.45382195673652465, 0.5951947464060791, 0.5021431497048829, 0.7221021982418614, 0.3396325925689876, 0.6405868458965019, 0.5906107671271521, 0.7983152254880688, 2.8707323318695073, 3.2564561378288532, 0.4789149745690643, 0.5214056592144963, 0.438166879227154, 0.5199445052991751, 0.6750718296318206], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.5469539666832948, 0.5650147784622814, 0.4956396109375141, 0.5415988588251338, 0.4774248353260239, 0.5469069627289954, 0.582088608051369, 0.5644284806881975, 0.5654308630741304, 0.453522231684812, 0.5191399201969022, 0.5257960192730178, 0.5470074294997319, 0.46856080575340553, 0.5117002412190603, 0.5109834998196058, 0.5653221083941462, 0.5318003031389684, 0.5531672357309017, 0.5754961887293365], \'SVC(C=1, random_state=13)\': [0.5752203853880767, 0.5561478572599988, 0.5493209082821467, 0.5658104853172694, 0.5386681669882443, 0.5400406859476976, 0.5701923508289755, 0.5820178449221477, 0.5583435328785353, 0.4951362345509244, 0.5293406089399951, 0.5798469731042455, 0.5949028085377802, 0.5403303708925076, 0.5509166984915542, 0.5410260469248327, 0.5517873547796363, 0.5400257534166675, 0.5442036238688869, 0.554296642923225], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.534254234771837, 0.5273872408839632, 0.48324870300022216, 0.5408277170907883, 0.4776672821186642, 0.5339482348660229, 0.5563932253073968, 0.5642858509064503, 0.5522514349208141, 0.4670997505657969, 0.504763735500974, 0.5009815493105495, 0.5580931489728133, 0.48158416985942454, 0.5114098646136128, 0.5598425599674474, 0.5399920066533174, 0.5323396001061841, 0.5533169890115125, 0.5749887413669309], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.344650878660001, 9.789634253834288, 10.234617629008575, 9.789634253834288, 10.234617629008575, 9.344650878660001, 9.789634253834288, 10.234617629008573, 11.569567754531432, 9.789634253834288, 9.344650878660001, 9.789634253834288, 8.454684128311431, 11.124584379357145, 9.344650878660001, 9.789634253834288, 11.124584379357145, 11.124584379357145, 10.234617629008575, 10.234617629008575], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [3.8312965916009603, 1.2757177041598182, 1.3063955640337443, 1.742010862478681, 1.7242527098582006, 3.4113419268037224, 1.7242527098582003, 4.726269084024941, 3.008502007205494, 2.162776231405763, 2.1241844063538013, 2.1627762314057635, 2.5906448613810387, 1.7449190855813075, 3.03917986707942, 4.733372345073134, 2.998490523054675, 1.7192469677827908, 0.911302312905178, 2.952795436954521], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.7661734745942168, 0.4656262819843586, 0.8797206186686329, 0.9203521485217185, 0.4360379906012338, 1.3088461138430836, 0.4570110952131942, 1.3499676866732122, 0.9226608461105871, 0.8325275391094544, 0.8579068602830657, 0.9558007680178079, 0.9605953314771317, 0.462674176974021, 0.48252984856728404, 2.1901837451565425, 1.7914572454950608, 0.8564388164678043, 0.9299035393392576, 1.704218229332607], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'poly\', random_state=13), SVC(C=1, kernel=\'linear\', random_state=13)]]"}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.5533409945100276, 0.49653406842263353, 0.45470016392746565, 0.5357250962620629, 0.5308675756695341, 0.5318662354265854, 0.9517284948693846, 0.5720059029556479, 0.49164859622955975, 0.8881190695122864, 0.5104529368556585, 1.3433106737670002, 0.8678877447866, 0.9150975788017638, 0.951361129616835, 0.44001961623385333, 0.49849779959901164, 1.3899643627535883, 0.9230549244649827, 0.5248538831121432], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.48013963802406173, 0.503913136154145, 0.4513851933773866, 0.46084079486297347, 0.48712449829804627, 0.4645055118244897, 0.4964247615423023, 0.4902817463683743, 0.46304834311624116, 0.4745804243077629, 0.5006032947972805, 0.4763404082564848, 0.44349523777411864, 0.510240993900472, 0.4857745840747887, 0.45989068842499714, 0.49071206759612823, 0.47640790458648363, 0.45283984485976897, 0.46684056598825574], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.4709196454143003, 0.49494272823473234, 0.44559228297595715, 0.46321950928953654, 0.46499781940823093, 0.46324216625490866, 0.4989417506763165, 0.4821206352769668, 0.4616573820927635, 0.4780748416409049, 0.506726783781038, 0.4603529597904755, 0.45462736007908117, 0.5093395240393098, 0.4799760308237565, 0.45488735230478017, 0.4768437498101793, 0.4684608513480061, 0.45216916988036343, 0.45839344445623165], \'MLPClassifier(max_iter=2000, random_state=13)\': [4.407392947257534, 7.180033651362842, 0.3512491867661633, 12.116053418974184, 0.47639512521046523, 5.956986061896057, 8.996938051687584, 6.642817543848968, 1.2942481588955865, 5.004704269077905, 0.9433947772382058, 1.3505536984458024, 1.1441897596056405, 1.4177993988052646, 7.684397047305952, 0.7206087652726014, 0.48765854242111345, 1.3364402607651322, 1.1693119951722357, 2.616928193129867], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4418850256493078, 0.5296828541817209, 0.8429988297935617, 0.4876313093039208, 0.43108395804677196, 0.4459548998896092, 0.7510591242995454, 0.533350544751543, 0.48446944993259766, 0.3837297237464982, 0.6227416610501949, 1.4501496665321356, 1.5805025113678908, 1.7899040249848734, 0.5017687051064457, 0.4466809910046243, 0.4351146718552623, 0.5835186773396576, 2.3638618245645153, 3.250098048590546], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.2523062045172548, 0.7948681047022833, 1.5109290617875089, 1.3772111529124917, 0.6396551168706854, 0.49986585583345244, 0.9547117482470198, 0.567644306642206, 4.671594497884774, 0.804765291640979, 3.5527964693462217, 0.37316326567387254, 0.9203998792118687, 0.8467659543354604, 4.646603554607988, 0.5435136265077525, 0.556583564157907, 1.3385727487559325, 0.6866200379453956, 0.3879051223489701], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.5628558907047433, 0.554181204586666, 0.5125097403222919, 0.5370070420047256, 0.509874125380322, 0.5169519828652325, 0.6098272689379775, 0.5679661855929746, 0.5116088287905614, 0.4839637656110109, 0.6002613304238374, 0.4799125732587339, 0.48526442568094563, 0.6273180486834572, 0.5400361691609362, 0.5464563340982266, 0.5856299086226011, 0.5337543664919878, 0.5670632101513736, 0.481073549693949], \'SVC(C=1, random_state=13)\': [0.6064079829117369, 0.6068449686082268, 0.5620335990938478, 0.5723411321771731, 0.5675601994905389, 0.5764219322209259, 0.6347368833640978, 0.6042143059620187, 0.5794223495208162, 0.5005797153356378, 0.6344542123069898, 0.5409776612425485, 0.45074335134021826, 0.6972368633539212, 0.5806111134636253, 0.5870266574929536, 0.6040475039393194, 0.596020872795128, 0.5884208441302977, 0.5117577731210439], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.5380928350028026, 0.5284297259070256, 0.5128725371051933, 0.5494438582518277, 0.4982013393721465, 0.5169264273867945, 0.6095109940377715, 0.5675292707081131, 0.5373420383162983, 0.47233280311905673, 0.6005146432211916, 0.4691301992060559, 0.49761152273374526, 0.6277619441874285, 0.5397736696026852, 0.5463877969831613, 0.5863380950113106, 0.5462655386670913, 0.5796082861258771, 0.46957807851856675], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [12.459534504880002, 10.234617629008575, 9.344650878660001, 8.009700753137144, 11.124584379357145, 12.90451788005429, 9.789634253834288, 12.014551129705717, 10.67960100418286, 10.234617629008575, 12.014551129705717, 12.014551129705717, 12.459534504880002, 11.569567754531432, 11.569567754531432, 9.344650878660003, 11.569567754531432, 9.789634253834288, 12.014551129705717, 10.679601004182858], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.199913944906412, 2.154218858806258, 2.653454692680204, 2.593553084483665, 2.6142194602067717, 5.256182777772812, 1.267160331560313, 2.6306907979843137, 3.465594385503382, 3.0748634690287555, 0.5063648743341679, 2.5806333772302192, 2.219126209078206, 2.203465575430508, 2.5856391193056285, 4.305503715097858, 2.1978164259336292, 2.6163169791795546, 2.609857125552832, 1.2913783378075159], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.360387595792254, 1.829085001972752, 0.5686653639749888, 0.9460681482279463, 0.4389462137038606, 1.4178410742194456, 0.8850191573689474, 0.9122032008904364, 1.347059463570585, 0.9559402001982865, 0.475777198315656, 0.901183766257636, 0.5132077084412099, 0.936223960785502, 1.7828998728955552, 1.7457043452232475, 0.48773283699483094, 1.7357506752440874, 0.8914650787317222, 0.901490495146489], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [SVC(C=1, kernel=\'poly\', random_state=13), SVC(C=1, kernel=\'linear\', random_state=13)]]"}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.9494481632309408, 0.8572953089249886, 1.383446694955207, 0.5856622471338215, 0.4908957062713748, 0.9884061150367532, 0.5088976306475035, 0.518649412735508, 0.4425389910162792, 0.4780119157720571, 0.9348734517331877, 0.8922670806318127, 0.9438233189937508, 0.9367197352192677, 0.9030319561633448, 0.5726493103771172, 0.5179692644110915, 0.5580371855045468, 0.5279350473072189, 0.5593546870674188], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.5373207139999512, 0.455466590836293, 0.4900931025996767, 0.48959217027054097, 0.4493145687837656, 0.49266026298907045, 0.4708298864770928, 0.48056344986281163, 0.4709521424716273, 0.4712054476760367, 0.4597291519332339, 0.4767359556039375, 0.5094730216188721, 0.4714101057735012, 0.48984777192009704, 0.481574660066949, 0.4827645369295002, 0.48029728262417015, 0.5142647618252185, 0.5114091149590138], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.5451855071888845, 0.46060131880324023, 0.4977454861651916, 0.48516239216782736, 0.45101634165798277, 0.4803493145543935, 0.46516455630423914, 0.46631231892491315, 0.4715967136055002, 0.4526907587582727, 0.4656051989973276, 0.4873490584529514, 0.4980010957321722, 0.463832888828161, 0.4851986393909828, 0.47727227981209064, 0.4912423928204469, 0.48004832516972656, 0.5168998382269271, 0.5136380372956091], \'MLPClassifier(max_iter=2000, random_state=13)\': [8.978823775282667, 4.588677967634678, 2.081548398435936, 2.115001700456233, 1.1781110266135995, 1.8662633563507949, 0.7889986644455501, 7.289659717141647, 1.1263333102724644, 1.2621304196860936, 9.000501274412901, 0.6233939041535903, 1.3801908884339678, 5.941246169851155, 4.9469552186113255, 7.43768200842868, 6.057541370798982, 1.0513988895698134, 1.5240462179213088, 2.3899697179833055], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.1614387896581313, 0.5027904779202558, 1.4833120253989072, 4.771759602897912, 1.1166636113898032, 1.9079908320704277, 0.49879293548652076, 0.5156809433364639, 1.3118085626567233, 0.5416901243851227, 0.5036567702086491, 0.4741757303581516, 0.5693285791680904, 3.025795511915403, 0.4857218442967036, 0.6198675022219043, 0.622774989986855, 3.1962492586330353, 1.5272351269432662, 0.4920864035740337], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.3676251559222454, 3.828902983710721, 0.8452520608510513, 0.5100865451220427, 1.316210464402765, 2.42675913546479, 0.5461288698283182, 0.5475803054770156, 0.3917105435487769, 0.5456416337882283, 0.6509356505329926, 0.6250249692465649, 0.6052395418162999, 0.6899105194698059, 0.6270479949425734, 0.6131848349758374, 0.7246611879083654, 0.48994206534369944, 0.7827097606246359, 4.1369163206895285], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.6399647288146679, 0.5782429161154176, 0.6251615856005155, 0.5672203096442244, 0.59319793290277, 0.5922681891865984, 0.5355186644807866, 0.5824789449010334, 0.5118233676594931, 0.5574342545105626, 0.5683840981802187, 0.5523573224330613, 0.5782803760841077, 0.5657926767844516, 0.5527764754944096, 0.6078923803199311, 0.607363187901965, 0.5158362316283587, 0.615886911044477, 0.5565690697715381], \'SVC(C=1, random_state=13)\': [0.6550649561112943, 0.5926943940303537, 0.598847262267915, 0.6192911318112388, 0.6449324637371977, 0.5849695432459574, 0.593637576500804, 0.6072015758081701, 0.5925925304322334, 0.5948600842027166, 0.6357012235934926, 0.5941953489890297, 0.6207539629327145, 0.5671102924700981, 0.5957768728044402, 0.6434779521009067, 0.5958454302492323, 0.5670769770107261, 0.637278559787778, 0.5950866918225086], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.6395775043358317, 0.5769640272692695, 0.6123433624283181, 0.5922088197028811, 0.6051556127773902, 0.5801858100992793, 0.523230375712659, 0.596971628829164, 0.5230700330658079, 0.558430102271099, 0.5679207654275158, 0.5644734609173067, 0.5778074522109876, 0.5535149834554014, 0.5650889967485818, 0.6209698961542588, 0.6071532233627288, 0.5025129276975221, 0.6039912507211842, 0.5440724570895589], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [11.56956775453143, 10.679601004182858, 12.459534504880002, 12.90451788005429, 9.789634253834288, 11.569567754531432, 11.569567754531432, 10.234617629008575, 12.459534504880002, 8.454684128311431, 12.014551129705717, 11.569567754531432, 10.234617629008575, 11.124584379357145, 11.124584379357145, 13.349501255228576, 8.899667503485716, 11.569567754531432, 11.124584379357145, 11.56956775453143], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [4.779878135303132, 5.582649751396961, 4.783429765827228, 3.9155835027530768, 2.6063054950287357, 5.616879241794981, 3.904117907050944, 1.7835109106332696, 2.5998456414020126, 1.7599363118075355, 2.203465575430508, 1.3170504556060325, 1.692120738432961, 1.7278043403822965, 4.314871791827208, 3.528404216802547, 1.2857291883106372, 4.340543909625725, 2.993484780979266, 2.6327883169570963], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [1.4123891710747045, 3.893700417971895, 0.9318616261315619, 0.9428371788566513, 0.897128160492549, 4.3753035991418905, 0.9150536098214042, 0.9399867699256838, 1.3075314344722488, 0.9265770196951955, 1.3855557383497799, 0.4890335841017177, 0.8609983974738817, 0.44119709712106986, 3.4993223207004047, 1.0236024091284346, 0.48013953296959616, 1.3797532244084745, 1.7596320029586747, 0.5061622615646767], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.3297313060586287, 0.5022051153370433, 0.5272720632377274, 0.502687193160503, 1.4302103679010383, 0.885873329056623, 0.531431685851693, 0.8806246393743845, 0.5757085771546618, 0.5028462019890038, 0.9548391072856945, 0.5014414380332383, 0.45563404720433137, 0.478414194933678, 0.47967388232489083, 0.8859745237134649, 0.5443896306287753, 0.5088593931238666, 0.4954357106294302, 0.5302125567536257], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.46663619712049415, 0.5032725016096049, 0.48701547014653496, 0.46789595926263855, 0.5504616497508685, 0.4643369031540448, 0.5025974334744973, 0.459453490051502, 0.5148023286300796, 0.463289755718362, 0.5113617046761596, 0.450604901748846, 0.4575644028373959, 0.44634328212223173, 0.4674912876860247, 0.46262784837803445, 0.49556247034091533, 0.4589771193439382, 0.4672363006929017, 0.4894236974976183], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.4627953756278185, 0.4803467541065393, 0.4794962220511172, 0.46898771062733824, 0.5386956374556899, 0.47142880508304796, 0.4917270328792927, 0.46412834752964727, 0.5019093448907997, 0.45315275740133854, 0.497136158056559, 0.45155225099596885, 0.46036025126466984, 0.449697351607175, 0.4822374892060741, 0.4548190695908191, 0.48402927816023966, 0.46760004584436815, 0.47281510156211237, 0.4694201719506286], \'MLPClassifier(max_iter=2000, random_state=13)\': [5.76147719901364, 0.8123262651120949, 1.933644385289468, 8.69643787726678, 1.3623190523274604, 5.090991245860325, 5.864610602792022, 0.6263381152717236, 3.4924626031441237, 4.870500020225078, 1.3517006293262552, 6.624380291242471, 5.5668746179361, 1.0044398212995589, 5.497262671210194, 0.6041755215807264, 5.9991360306708446, 7.582934486031496, 3.0332510889977393, 7.41611896173856], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.4825893710925593, 2.0442608185769817, 0.6689131478117806, 0.7819248355706457, 0.7819253650512885, 0.7935493220141632, 3.03814403849175, 0.4613449544362245, 0.6539397488121563, 0.5149941661413453, 1.8911472403663827, 0.3917666862453332, 3.0805441445722064, 0.46397195094699567, 0.4849315315980276, 0.4398736961016312, 0.6796529441445668, 2.183176733292357, 2.0279578820636184, 0.6090794073978922], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.4944218306361311, 0.5715782987789221, 0.6829127239091277, 0.5780393032115052, 0.6975820132263193, 0.48946090277730037, 0.5395112902549135, 0.8998934949601997, 0.7677742107552115, 0.39918651691412776, 1.1585381346302228, 0.3914519184275907, 5.104046990345675, 0.4782464963473856, 0.5141745520994787, 0.5134886460967567, 2.7356061514133847, 0.6262688350361058, 0.413233286989172, 0.6428862964612134], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.49211263339819433, 0.567625010440826, 0.5906543100540211, 0.592498655938098, 0.6498069661558469, 0.5833626728030742, 0.5292134392902005, 0.5140976710124259, 0.6242111458512125, 0.5248656384661574, 0.5744858496883876, 0.5166221497208863, 0.5270219174791353, 0.49997626086508856, 0.5634852969039692, 0.49575876681248515, 0.5567570735231421, 0.5676262481032375, 0.5519964298999406, 0.5505169242098833], \'SVC(C=1, random_state=13)\': [0.5377668033299814, 0.6373007365406143, 0.6060727497473606, 0.5554220006558742, 0.6676190073223972, 0.6192798481440541, 0.6091332576436209, 0.5541122303654918, 0.6232017817552727, 0.5351166414816364, 0.647002702371878, 0.5536563917400319, 0.5424363469107829, 0.5542389173669985, 0.5914242749941687, 0.5497879304668113, 0.6099172686393646, 0.6204680525994791, 0.5685028581824249, 0.5520649598346492], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.5045851380903577, 0.5925232250229139, 0.578321013576603, 0.6048666347879419, 0.6628489874104153, 0.5842855916003179, 0.5549858617505111, 0.5144449877357828, 0.5986016958993214, 0.513732017757615, 0.5664877991975071, 0.5157731171271713, 0.5269932470829841, 0.500457716258586, 0.5634173209131458, 0.47113460821487163, 0.5680900286266133, 0.556088446037453, 0.5649043183356104, 0.5257765183267431], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [11.569567754531432, 14.684451380751431, 8.454684128311431, 10.679601004182858, 10.679601004182858, 9.344650878660001, 11.569567754531432, 12.90451788005429, 9.789634253834288, 10.234617629008575, 12.014551129705717, 11.124584379357145, 10.67960100418286, 13.349501255228576, 10.234617629008575, 11.124584379357145, 12.90451788005429, 9.344650878660003, 12.459534504880002, 12.904517880054291], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [2.657649730625769, 2.1456614862067527, 3.029168382928601, 1.3320676818322608, 2.2406032889311573, 3.4019738500743726, 1.3206020861301286, 2.1842533112587144, 1.7684936844070411, 2.1627762314057635, 1.7392699360844288, 3.8569687093994767, 1.742821566608525, 2.579179265678906, 0.4721353839361458, 1.7278043403822965, 3.051288870203021, 3.5012779874527165, 1.7684936844070411, 2.2120229480300138], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.9207027593182826, 1.3689589006557075, 1.7294441860617915, 0.49855502527549383, 1.0193118209101015, 1.3264886381202456, 0.48963310961547607, 0.9031418530499402, 1.3143857808032464, 0.9120059545382987, 0.9536893167810772, 1.3307554225014184, 0.5109707572879487, 1.2948229058348886, 0.4802789651500747, 1.361630528727482, 0.8924291473059929, 1.8527990329789645, 0.8939410730289654, 0.9155436527984468], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [SVC(C=1, kernel=\'poly\', random_state=13), SVC(C=1, kernel=\'linear\', random_state=13)]]"}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [0.48012336700878794, 0.4641988835348916, 0.9080245901236256, 0.5068514573134862, 0.8770120497603012, 0.5468811408833049, 0.4760318444895732, 0.5263681296046245, 0.49995140972779695, 0.8701664927317057, 1.3368616074858977, 0.5288493539360621, 0.44018691294222817, 0.4436453139630654, 0.4653219609376629, 0.5364756654507392, 0.467666073858131, 0.519013131647201, 0.4988013835695369, 0.8861609827199823], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.41412505615259826, 0.43585885296918625, 0.4460543687508004, 0.4640167082649289, 0.4640724129828241, 0.465367707440027, 0.45857178848677266, 0.4761465126707047, 0.47718614991297653, 0.4220114986614098, 0.4534429799589544, 0.5087218128893848, 0.46080733762949344, 0.46646824142151944, 0.44826598762528314, 0.482691872849937, 0.48473422975826497, 0.45091425514965555, 0.5198725171048085, 0.4328250651085418], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.4220865832984423, 0.45398111062572777, 0.45086503032497904, 0.45283311225852463, 0.47788732384657484, 0.4520548126792652, 0.45662279496871677, 0.48176084223305776, 0.47802067941487675, 0.4286164850877819, 0.4634463918459644, 0.49484191524789833, 0.4606153974440306, 0.46625008690631026, 0.44050821780706323, 0.48977840579534143, 0.4812188020905534, 0.44906995957242735, 0.49878081740340025, 0.4450210158610685], \'MLPClassifier(max_iter=2000, random_state=13)\': [0.3719127401115828, 0.9271847978607831, 0.7162411334983798, 3.6208688948543535, 7.572015493033243, 2.1828115992649653, 0.9462206336760574, 1.4385168597271014, 0.8396644156259878, 3.6606607757829446, 0.681970354038777, 0.702759905206444, 1.4879336926873092, 1.459416680853379, 0.5655680675691006, 1.789385501310566, 0.6664473481436461, 0.5275397525070169, 1.009582895397952, 5.060519967667833], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.3666203971817525, 0.48246629718033407, 2.9875678583877576, 0.6289014893291228, 0.7753163356716251, 1.9708190671100505, 0.5024680287322868, 0.6693175368851885, 4.823512736601244, 0.9527555295876449, 1.3796346134341542, 3.5251031495260254, 1.6734993344003608, 0.5002741954256522, 2.434512567914482, 0.4452582599888358, 2.963551164541418, 1.7092243977042254, 4.084317396824808, 3.0176732997306472], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.3650951147241029, 0.5060193259510218, 0.5973643612686588, 0.5631057901665083, 3.8157369075624294, 0.5084564183581348, 0.613597970116625, 0.7666170552538538, 0.539397793311692, 0.6578858618672041, 0.6729354705866101, 0.5130856495029913, 0.9373599227568753, 0.46824454565065793, 0.4307464725846885, 0.4121301907954542, 0.48675636024709973, 0.49729236147730044, 0.6445510315562053, 0.5259906625910512], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.4583981660602251, 0.5475594205278997, 0.552560429172596, 0.522607552861004, 0.5866478257060401, 0.5506345984941187, 0.5481992250386192, 0.5614221186138507, 0.5925071758209937, 0.5482312312430627, 0.5329060811062817, 0.6336599401074936, 0.49801529139342404, 0.5260663520803555, 0.4828567036563454, 0.5290841581723115, 0.5423225667484354, 0.4834601917324988, 0.5732574862223778, 0.543898150470975], \'SVC(C=1, random_state=13)\': [0.5008564074508794, 0.5560249540176495, 0.5785417862710076, 0.5542714431128382, 0.5708448716443201, 0.5701077099561149, 0.5669323457135302, 0.6001420283258911, 0.5720293823164454, 0.6064135697209416, 0.5920568925016335, 0.6248053810172451, 0.5662674846826747, 0.5302363740763979, 0.5643412326476306, 0.621258070891408, 0.5911433022584068, 0.5292846895314544, 0.6278156832536066, 0.5918020746038315], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.45877140953414064, 0.5218673115961573, 0.5525748082389775, 0.5113093107324578, 0.5633749854217791, 0.57543232576707, 0.5480659685106958, 0.5615934101551969, 0.5674756594769018, 0.5745326545155169, 0.53489674394039, 0.620681625833759, 0.5178884037022069, 0.5262932662356653, 0.47080102252932415, 0.5289956828729973, 0.5412458016147836, 0.484124128772577, 0.5611106451959147, 0.5324269826497889], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.344650878660001, 10.234617629008575, 10.679601004182858, 10.234617629008575, 13.349501255228576, 10.234617629008575, 10.67960100418286, 12.90451788005429, 12.904517880054291, 11.569567754531434, 6.674750627614288, 11.569567754531432, 9.789634253834288, 9.789634253834288, 9.789634253834288, 10.67960100418286, 11.124584379357145, 11.124584379357145, 12.90451788005429, 9.789634253834288], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [0.8941875677061673, 2.1727877155565825, 2.1763393460806784, 5.569086636722045, 2.2005573523278814, 3.041277386052203, 2.1577704893303538, 2.612121941233989, 2.626328463330374, 2.1949082028310025, 2.1506672282821615, 3.88554905030062, 1.7449190855813075, 2.1542188588062583, 1.2556947358581805, 3.539869812504679, 1.2828209652080105, 2.639891578005289, 4.849791227650489, 5.621241576448923], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [0.45090185238303543, 1.3440696224591389, 0.4752732230746652, 2.1732223644019584, 1.3396634058974881, 0.542292024583344, 0.5054471077076004, 1.7832504836921195, 0.45359889686957655, 0.9491436680389478, 0.9497870754604169, 0.9275132237415699, 0.8890886953979822, 0.8576001313942123, 0.40821053965827564, 1.41658420902027, 0.8632492808910913, 0.9233181857960044, 0.5737666563231658, 3.1014742109136386], \'removed_models\': "[[RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13), RandomForestClassifier(n_jobs=-1, random_state=13)], [SVC(C=1, kernel=\'poly\', random_state=13), SVC(C=1, kernel=\'linear\', random_state=13)]]"}'}</t>
+  </si>
+  <si>
+    <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: 'SVC(random_state=13)WITHOUT log_loss_field', 1: 'SVC(random_state=13)WITHOUT log_loss_field', 2: 'SVC(random_state=13)WITHOUT log_loss_field', 3: 'SVC(random_state=13)WITHOUT log_loss_field', 4: 'SVC(random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
     <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf5088550&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf56f9e90&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc042d7c90&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf065c550&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc042d7550&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc042d7510&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc05188410&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc042d7410&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc042d7390&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc042d72d0&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc042d7190&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc042d7010&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f21798c0290&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f21653b4c10&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2164f9d990&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f21648e88d0&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216fb37d10&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216fb37910&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216fb37a90&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216fb37890&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216fb37710&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216fb37690&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216fb37610&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216fb374d0&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f30a5641b10&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f308ed25410&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f308ce18090&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f308df3fa50&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f308ce0f350&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f308d1f77d0&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f308d6dfc50&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f308c154150&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f308bebf050&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f308bebc9d0&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f308bebf650&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f30a1b56b10&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e5a61ad90&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e5a5f6c10&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e5ba212d0&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e5ae138d0&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e5b01e110&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e6ee8f590&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e5a654d10&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e5a654810&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e5a277b50&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e59ef10d0&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e59ef3610&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e5aab9cd0&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe210f3c2d0&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe2116a0b10&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe21080b150&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe210ae0650&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe211376110&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe210ad39d0&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe210f1f710&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe2107f2390&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe2107f0190&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe210f08590&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe210f085d0&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe210a8d650&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f21659653d0&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216ad52910&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216ab04e50&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216ab2bdd0&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216ad4d650&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2164910910&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ad7af90&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ab66ad0&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ab56710&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ab39950&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2160ec39d0&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2160ec0290&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f308bf65290&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f3087525b50&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f308bf920d0&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f308bf55dd0&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f30a1b663d0&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f308d1f69d0&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f308bf85410&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f30971b7d10&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f30971b7810&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f30971b7990&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f30971b7910&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f30971b7a10&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb290290&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf508b890&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb27d810&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb298dd0&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc0ac6ff50&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf50ac9d0&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb298410&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb28cb10&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb28c950&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb28da10&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb28d310&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb2a9250&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe211375d90&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe211b77190&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe21086ef50&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe210878410&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe20beb5fd0&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe2108cef10&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe2108cd690&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe2108cecd0&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe21baf7b10&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe21baf7d10&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe21baf7a90&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe21baf7a50&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e555c54d0&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e55586950&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e59f84750&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e5aa73410&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e555af3d0&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e59f75050&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e59fabc90&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e555646d0&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e55566f90&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e55567710&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e5a61a210&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e5aa41950&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68f54450&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e5560a910&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e55612190&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d4b410&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68fc7510&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68f3b710&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68f3b690&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68eb83d0&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68eb9190&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e5560b050&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68eb8e50&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68eb8e90&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f145211b250&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f145202e910&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1452038190&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1452025650&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1452174c50&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1452174250&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f14448ab410&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1452174490&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1452174350&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1452174310&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1452174110&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1443c0b050&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5495975c10&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5490901210&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54908d8290&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5490918410&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54952a9390&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54952ab650&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54952a9190&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54952df190&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54952dd990&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a456fdd0&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a456fb10&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a456fb90&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc040a0250&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc040d9250&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb360e50&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb360dd0&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb340550&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc040ddd90&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc04108410&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040d0650&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040efbd0&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb450e90&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040edf90&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc04107190&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f37c0c8d450&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f37c5000f50&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f37abf10750&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f37acc49910&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f37ac7c4290&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f37acb80b90&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f37abfcbf50&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f37abfc8690&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f37b1f1f290&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f37c54daa90&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f37c19c0f50&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f37c19c1150&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216adcb290&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216adb5d90&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216adc46d0&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2160ef3dd0&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216adb6210&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f21648ea890&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f21648e9150&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f21648e8910&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f21648e9110&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f21648e8a10&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f21648ea990&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f21648eb410&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68d35a10&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e691fef90&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68d20dd0&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e691ff710&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d161d0&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e59f8d010&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e59f8e690&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e59f8c910&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e59f8e190&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e59f8ff50&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e59f8c090&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e59f8f390&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf5070250&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc04063710&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf0650490&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc040a0dd0&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc04096650&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc0405c550&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc0405c9d0&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc0405d790&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb47e350&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb47e310&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb47df50&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb47e250&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe20bea1550&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe216af8dd0&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe216adfa50&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216ad8410&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216b20590&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216b36c50&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216b0f010&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216b0e910&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216b0f8d0&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe21080ab90&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe210809290&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe21080b110&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1443801cd0&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f144441aed0&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f14430b1090&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f14430999d0&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1443099290&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1443fd2410&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1443c0bb90&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f14448ab410&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1451de3350&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f145c844550&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f14536211d0&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1458d54510&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a41e0290&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a41f9a10&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f549097f190&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a41f8410&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5490995490&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a4054950&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a43179d0&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a4317cd0&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a4317650&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a4317890&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a4317950&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a4317910&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d445fc250&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d35f0e810&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d445ee190&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d35809dd0&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d357996d0&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d366550d0&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d44847c90&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d44844650&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d44845d50&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d35f39f10&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d36b4af10&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d450ad710&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0de58be250&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0de6384690&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0de0e62950&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0de586edd0&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0de0eccb10&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0de58a1890&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0de58b6410&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0de58a0d10&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0de58a06d0&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0de58bec90&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0de58a2510&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0de0e9d390&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb410290&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc040fe910&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb3f0550&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf06c0dd0&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc040fc910&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb310b10&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb3f8410&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb311310&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb313d10&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb3112d0&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb311250&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb313e50&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f24095ee550&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f240a076510&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f24096d99d0&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f24091e1510&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2409dccf90&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2409a84bd0&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2409ad9350&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2409ad9c10&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f240964fb10&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2409673b50&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2409ad9b50&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2409b0e450&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f14523b3290&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f143e720550&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1451eca390&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1443f22910&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1451eb4b50&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1451eb1950&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1451eb3410&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f143e759390&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f143e758710&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1451ecbc90&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f143e7584d0&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f143e758050&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe20bea70d0&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe20bf39950&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe20bf2f590&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216c68410&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216c65950&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216d9e190&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216d9dcd0&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216d9db50&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216d9dad0&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe20bf38250&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe216d9df50&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe216d9d010&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68f7dc10&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e5563fd50&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68f5b710&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e5563d650&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68e92210&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68fdddd0&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68fdd3d0&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68fdd410&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68fdde90&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68fddf90&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68fdd450&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68fdd510&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc040c9210&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc04086650&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc04098650&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc04086950&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb4859d0&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb2c19d0&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040c0410&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb42f610&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb42f4d0&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb42ee10&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb42ff90&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdbfb42ffd0&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216adb3290&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216adf2210&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216acd2710&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216adf3dd0&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216adc1890&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216acd2bd0&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216acd35d0&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216acd3290&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216acd3490&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216acd3250&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216acd31d0&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216acd3bd0&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d4ef81250&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d3583e0d0&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d357e4fd0&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d30e90550&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d358091d0&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d35808490&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d30e59410&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d3587f950&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d362c1850&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d44adfed0&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d44adfd50&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d44adea50&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68ed6f90&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68d981d0&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68d940d0&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d8b410&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d00b10&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d02410&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e5560bc90&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e5560a210&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68d81950&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68f3b250&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68f2be10&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68f2bbd0&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a4307b90&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a42fe690&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a4326510&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a42c0410&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a42e5190&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a41d4950&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a42f1210&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a42f0650&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a42d1050&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54952bbe90&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54952b8890&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54952ba510&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf06a8290&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc04142c10&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc0413da10&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc04060dd0&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc040ed110&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc04070650&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc04118410&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040ffbd0&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040fcb10&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040fcd50&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040fc190&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040fe750&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0de672a190&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0de5f1e1d0&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f0df4c2f2d0&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0de8b259d0&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0de580c290&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f0de5f888d0&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0df452a8d0&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0df597f310&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f0dfe9d6190&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0dfb498d10&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0dfb498e50&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f0dfb499490&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68e7da10&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68f82210&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68fa3710&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68f73410&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68cf9950&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68fc00d0&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68fa3c90&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68f96d90&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e691ff3d0&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68fa3250&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e5562de10&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e5562da90&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1443153290&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f14437e7fd0&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f144314a210&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1443099490&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f14523b2950&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f14523b3b90&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1443fd3410&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f14523b3a50&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f14523b3bd0&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1443133c90&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f14523b3c10&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f14523b3850&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb490290&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf0661950&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf0687590&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf06b0dd0&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf0677190&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdc040b1610&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb4a0410&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040b0c50&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040b0c90&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040b1810&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040b1790&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040b0d90&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216ad3b290&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216ad3d650&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216ad2a210&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2160ebe990&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216ab0cc90&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216ae015d0&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ae01cd0&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ae01710&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ae01690&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ae01a10&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ae01910&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ae00b50&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe210a8e550&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe216da6f10&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fe216c5ec50&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216d90410&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe210809210&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fe216b0f190&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216b32590&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216b33910&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7fe216b339d0&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe216b33950&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe216b33cd0&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fe216b33bd0&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68d2a810&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e55565a10&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68fc7710&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d5b410&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d12210&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68fb0190&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e555ce150&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e555ce850&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e555ce350&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e555ce790&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e555cf210&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e555ce750&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2160f6c490&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216ad02210&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f216acf1950&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2174dc3dd0&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216ad007d0&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f216ad3cf90&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2160f0bd50&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ad3c0d0&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f216ad3fa90&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ad3d2d0&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ad3cd90&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f216ad3fe50&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1452153290&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1443141890&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1452161490&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1443ca5c10&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f145217c390&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1443375090&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1451ee2a50&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1452136910&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f143e7de8d0&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f143e7dea10&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f143e7df350&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f143e7de490&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc04068250&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb448710&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdc040860d0&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb458dd0&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb441ed0&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf0719790&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbf0718410&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb4399d0&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc040ada90&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040ac250&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040acc50&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040ad850&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54959dd8d0&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5495dbb490&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f5495e12350&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5495580d90&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f5495ddc550&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f549730a110&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5495dcd490&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f5495dcf390&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54aaf0b350&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54aaf0b050&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54959ddbd0&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54aaf0b450&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a407e690&gt;: [1.031513960592658, 0.517960065310857, 0.965507841227086, 0.5239807405604324, 0.4936414892732486, 0.5042137048426558, 0.5877767351851573, 0.5005605796373103, 0.4407491531863026, 0.5212623346845037, 0.477535419960667, 1.0140531730423807, 0.4960904075118537, 0.4808449664338186, 0.4703331255737202, 0.49030208647397977, 0.5273527085082461, 0.523197087999558, 0.6483088200192761, 0.46260370128870854], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54a4081c10&gt;: [0.45106727242425293, 0.5203214944587643, 0.4636852422405205, 0.4753664524333461, 0.45511460008507865, 0.4475448665253321, 0.5464338626032057, 0.49975786398067146, 0.43925159680754916, 0.5016263168524328, 0.4573003446824231, 0.4581490033222797, 0.4664996841632425, 0.49294617415858366, 0.47555292288505907, 0.4816476630088362, 0.4513080013063892, 0.4942817726560421, 0.5367357481548007, 0.45424370812963855], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f54908d5dd0&gt;: [0.46637475491147184, 0.5046059105689995, 0.44844750245614456, 0.4696679010834588, 0.45681868774384565, 0.46458292846013194, 0.5311309056736813, 0.49651307454165483, 0.4382099487819444, 0.4807837610860337, 0.44071579459099663, 0.47177937051566804, 0.45801254827232796, 0.4735698912650946, 0.4778823656609843, 0.46935612893762646, 0.465242675850864, 0.5060864971597159, 0.538896132216067, 0.44498287723212776], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a405fc10&gt;: [7.525943930879382, 0.7018883191882103, 4.697754337316328, 8.936586164501158, 6.990229259766311, 1.4558773633028974, 7.0139683440321186, 8.403337038308521, 6.4367140159326715, 0.8600286643081129, 5.244390065642306, 8.713948161331324, 1.1520450452764925, 0.569658660528747, 9.484637932079501, 4.825941558782773, 5.664489308117955, 8.237013391808004, 6.393387261013215, 0.39805609457623053], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a4055690&gt;: [0.5086859278292639, 2.321777365044519, 0.5392028534143154, 3.824398111079879, 4.138482212203943, 3.222687580829482, 0.8219314447016391, 0.7626811338778965, 0.31841659214183476, 0.5579832348867292, 0.34550290086062735, 1.3999492417957384, 4.461291870231905, 0.4852826496595791, 0.4381058144338622, 0.5151523894359801, 0.5542874172478295, 2.806578390489958, 0.7285850789503578, 0.42898782035823974], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f54a4056b10&gt;: [0.7872794263780075, 0.4396750599417181, 0.6084653816966942, 1.0829126779835314, 0.730660711571375, 1.6318721217219105, 0.6726498559379773, 0.8712767842484495, 0.33232394206680127, 0.5677775826552017, 0.3675809792074502, 1.145309991694977, 0.45784496223625504, 0.434899133088605, 1.496253780498508, 0.5397379885987351, 0.5723273249798492, 1.9416199707257817, 1.2093118752948102, 0.5171416716042637], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a42c0290&gt;: [0.522306639813832, 0.5236765382209189, 0.5348133710516381, 0.4392675349490902, 0.5188160903098704, 0.5131011927989786, 0.5592142574908423, 0.6119150068224979, 0.4517142079094854, 0.5510046034029179, 0.47599817475729217, 0.5416339548862967, 0.5059150419011095, 0.4917662573968164, 0.5405266780321387, 0.5101568759673748, 0.6173681004563765, 0.5756766975324006, 0.568550958748494, 0.5403009141875978], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a42c0390&gt;: [0.5970871613846579, 0.6222708432437853, 0.5935490949089833, 0.5371629865582488, 0.5645825895125035, 0.5533033353494334, 0.6862005087414682, 0.6524674861034216, 0.5495262322320075, 0.5961532318157468, 0.5496498723493956, 0.6252961504335102, 0.5629970235415322, 0.5976574578277822, 0.6113646659848057, 0.582873487459312, 0.6254254914483847, 0.6114640145362009, 0.6181924901895661, 0.5673226685988824], &lt;method-wrapper \'__str__\' of SVC object at 0x7f54a42c0fd0&gt;: [0.5220937641024846, 0.551956974180445, 0.5337686809900578, 0.4258660502434117, 0.5056038684891673, 0.5122970533708826, 0.5724967222904055, 0.6516137264020304, 0.4513355959874008, 0.551112446690302, 0.4753816992348072, 0.5281122754838672, 0.5199252747637232, 0.5061647820103325, 0.5535394598048554, 0.5101858773685399, 0.6161383306112062, 0.5769615842259287, 0.5693780032290964, 0.5405349852731413], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a42c3650&gt;: [12.515157426776788, 11.513944832634646, 12.014551129705715, 10.01212594142143, 11.013338535563575, 10.01212594142143, 10.512732238492504, 14.016976317990004, 10.512732238492504, 10.512732238492504, 11.013338535563575, 12.014551129705717, 8.009700753137146, 13.015763723847861, 11.013338535563575, 10.512732238492504, 13.015763723847861, 12.014551129705715, 10.01212594142143, 10.01212594142143], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54a42c28d0&gt;: [1.9043596640862341, 0.9465628731275485, 0.48846033709385966, 0.881533272750823, 0.9867069253205507, 1.3579778549873245, 1.44716917019862, 5.344297976556162, 0.8967917767601025, 2.830915613677208, 1.9212540435907408, 2.8100256498330936, 0.4130798591935377, 1.4086609935008454, 1.37015281680307, 0.8742659374207599, 1.9855598106183132, 1.365245190317388, 2.356830740285087, 0.9369358289531048], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f54952e59d0&gt;: [0.4604626216677113, 0.5021350552990774, 0.4925998313845558, 0.42290018046524414, 0.49161164277550085, 0.444480284309279, 0.509904321832139, 2.983422661574935, 0.4674342541439892, 0.9861270019224856, 0.5071838691908569, 0.429631891243076, 0.4225214171160512, 0.9740170810498563, 0.9538015834087196, 0.4478014024459088, 0.5604642924918543, 0.4188552289794613, 0.9554374589039472, 0.501568083152963]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f37abd4e250&gt;: [0.9739027709172952, 0.5623288810891273, 0.9364079815236419, 0.5790335605289464, 0.47031166594503937, 0.46401823873812564, 0.5700725858600444, 1.0295948810745452, 0.6500931600201054, 0.9567309732216422, 0.5208777855035714, 0.46412890776103094, 0.4930556683641507, 0.5350060842870074, 1.4440539259468828, 1.082622618735849, 0.45410742644045243, 0.45277360373109343, 0.5770131358527868, 1.0153465894033458], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f37ac3d2710&gt;: [0.46915496896487024, 0.4717782594445279, 0.4503236931408979, 0.5061130225273488, 0.4653411886971399, 0.47269917377456927, 0.4921378872119695, 0.5043805698771406, 0.5206327445346126, 0.4595208086085392, 0.48530148106061843, 0.5190008584667071, 0.4706450946631575, 0.47762073399277266, 0.4829050063766296, 0.5310612657632263, 0.4735868909925516, 0.44147513172556574, 0.4946746508343426, 0.49522091211455177], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f37abcc2e50&gt;: [0.4624446069309687, 0.4617463725684314, 0.44612964972814695, 0.48402459804473097, 0.46269674340763545, 0.46623275064399805, 0.47990576650236566, 0.49601224757122214, 0.49074818968857, 0.4694389888682543, 0.47736506767486886, 0.516500760217465, 0.49417065887159545, 0.4729699271827419, 0.48913860310321966, 0.5127426203305316, 0.47572600627500855, 0.4425819656964213, 0.48804001144772197, 0.4854303179338927], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f37abd46dd0&gt;: [9.006045768656554, 0.9713677954239864, 1.1833596910357675, 0.39632165725708757, 0.5840872773447701, 1.3747460998179477, 2.602871575654784, 0.8364398385745752, 5.429371347149697, 7.782609173171197, 1.6023176283911884, 3.136261234210445, 0.7390663971431028, 7.301290190839996, 1.1897812729696056, 4.334616811385086, 4.18653361680279, 4.8923141093122915, 3.952543735679563, 6.96248845043666], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f37ad2ca4d0&gt;: [0.8035775175336384, 0.6005604612390295, 1.9411613199720175, 0.35700746330273886, 0.4854272170271239, 0.5436316625638847, 5.392633727367164, 3.5245571011533303, 0.6429690820253308, 2.0652926393921107, 3.6946437668352083, 0.7612744981411479, 0.725038114026224, 1.7313037979297627, 3.7899921626650013, 0.7117432503738859, 1.4457647231657926, 0.4367408571433738, 0.6838066160614255, 0.6063957585849408], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f37aeb51410&gt;: [0.5631058400115296, 1.0148222442266979, 0.5405243797466428, 0.35230357162263004, 0.5296047696656156, 0.5434530979150975, 1.1885998978914074, 0.7544922472915787, 0.513908188466607, 0.9164557089791643, 1.2108048280828898, 1.0688494397713701, 3.7346578831260664, 0.7071467113754744, 1.9375472456250205, 1.3381727519516424, 0.4695513386880028, 0.7632870524181935, 0.577471532627114, 0.8242261341537018], &lt;method-wrapper \'__str__\' of SVC object at 0x7f37abd36410&gt;: [0.5743700725127798, 0.5365967496716897, 0.4742940617088368, 0.5024522859446469, 0.5211201263971385, 0.5014009814370518, 0.6072446340975294, 0.625444661434788, 0.561544124093693, 0.5824653435481736, 0.6012414812377573, 0.6620613020479307, 0.5397879615983084, 0.561820543951247, 0.5864590304339304, 0.5855744102062389, 0.49124206625200145, 0.5570713240521137, 0.5975999403078895, 0.6088272339580422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f37abcab590&gt;: [0.575327355340179, 0.5549103847691514, 0.5528524818706803, 0.546356548616347, 0.5942817534078575, 0.5619788875142679, 0.5938780717051659, 0.5954674614046116, 0.624971979378278, 0.6120593977611974, 0.5942694560432585, 0.6474449938492266, 0.584827951922176, 0.5718962734205855, 0.6276261980525669, 0.6783179207283627, 0.5797349401205247, 0.5832617443488554, 0.6113212428572182, 0.5653630070363422], &lt;method-wrapper \'__str__\' of SVC object at 0x7f37abd0b250&gt;: [0.5728167304248579, 0.5227130889010263, 0.5169367886396515, 0.5167929358605365, 0.521043407237214, 0.5427196124420323, 0.5922902673735172, 0.6243876801021931, 0.5621314157383486, 0.5815597024293668, 0.5884798885507361, 0.648093919184769, 0.5380643555227463, 0.5629462120294542, 0.603629907582735, 0.5853949357651351, 0.4781166719287997, 0.5721069578805218, 0.5824824443546659, 0.5941675514519026], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f37abd0bd90&gt;: [8.510307050208217, 11.013338535563575, 13.015763723847861, 8.510307050208217, 11.513944832634646, 8.510307050208217, 10.01212594142143, 11.013338535563575, 10.512732238492504, 10.01212594142143, 12.014551129705717, 8.510307050208217, 10.01212594142143, 9.51151964435036, 9.51151964435036, 13.516370020918933, 12.014551129705715, 8.510307050208219, 11.513944832634646, 10.012125941421433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f37abd0b710&gt;: [1.839330063709509, 1.3950383649867932, 2.3511992804502513, 1.4295509573449598, 0.4588553712213756, 2.8309156136772082, 1.4535244633826083, 4.761767699603859, 1.4319106661893406, 1.8642156118932316, 5.264009872170158, 3.3251666175642907, 2.341572236275808, 2.3913433326432543, 2.372813077643519, 3.9124163122053557, 1.8803861580485857, 2.8790508345494263, 0.4684824153958193, 3.3949156356297774], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f37b7003c50&gt;: [0.9790322015924026, 0.9532996522057213, 1.4191714547724716, 0.47921477881360036, 0.4677793241439492, 1.9164409599099714, 1.046988482959623, 2.9179986240520743, 0.518619323860508, 1.4191714547724716, 2.437937220825158, 0.9409027882438207, 1.9143031532117456, 0.509731786832159, 1.4385824043243973, 0.5682335590249158, 1.4306562765882975, 0.9556099939039271, 0.45815227996950547, 1.4930885921775459]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e5a188250&gt;: [0.48866882184444965, 1.4877499592204504, 0.5973393025168288, 1.6244046399666834, 1.4401753605622634, 0.49739688680406297, 0.4841770921335825, 0.6057835993532126, 0.5119965984073056, 1.0756452004278316, 0.551628267331763, 0.5002715897826859, 0.6099087014787092, 1.0022206703608976, 0.5081174689223419, 0.9703504267696521, 0.9289129582156848, 0.5417584254828279, 1.0374910545277976, 0.49006768549692503], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68d56950&gt;: [0.5193022596523931, 0.5254443209976506, 0.5659042837760107, 0.5593220536907988, 0.4903765442948531, 0.4530421723261455, 0.4662894510411747, 0.4783119385265965, 0.43857245123734695, 0.5010866363000033, 0.4966641438026035, 0.46704065798619215, 0.5354659562570688, 0.4698227821670025, 0.4933771998626509, 0.4708367291525551, 0.4464386149176869, 0.49803116413190185, 0.4801522078094036, 0.4982587639701157], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f9e68e83dd0&gt;: [0.5106794316801944, 0.49095909639279356, 0.5570782356843595, 0.544203255155666, 0.4814475970050739, 0.46371860326905434, 0.4462739803764478, 0.48942858862713545, 0.4509344815395971, 0.48733433641787155, 0.4889914303499062, 0.4669522719420535, 0.5198192340378296, 0.4563494206713456, 0.48550574087105797, 0.46669609499636866, 0.4563013481411059, 0.49351565361235494, 0.4797972347036402, 0.4769214004882561], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68d55a10&gt;: [5.368595396842532, 12.59619331452028, 7.683408066566709, 5.756419377184203, 0.9517246180077701, 2.7548548231253545, 0.6442261809735729, 1.6306559637337132, 0.5287815383281746, 3.5268303328838786, 0.8066233437357778, 5.544343352918306, 0.8145220357235482, 4.515867003448733, 4.579767793482841, 12.001884793323326, 1.5977731625400324, 11.859850390775417, 0.962835224421439, 5.32930637043986], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68e9a210&gt;: [0.6175548216570274, 0.7318983062915938, 0.8306071446585693, 0.6130059296559044, 0.8435397475147407, 4.083523039452189, 0.5063805331300791, 0.5993172844130604, 0.3434050335783993, 0.5129418494504357, 6.068679376734951, 0.7053525826269037, 3.0438962642625444, 1.0999935156442124, 0.4876172182366168, 0.5976209331476624, 0.5288434114148982, 0.5034837814832351, 0.5249210752556233, 0.8396054502757695], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f9e68e9b6d0&gt;: [1.855056756946528, 0.8511138407841305, 0.9446900990877608, 0.7265277560428841, 1.1331703987258543, 0.9058789522485802, 0.3960372500004674, 0.5431655812887084, 1.9690543474822273, 0.6020150090379062, 6.990355128099957, 0.8036964634389773, 0.5106533997101752, 2.0397241626364337, 0.5375501613805433, 0.5888934657881986, 0.5042403785462902, 0.4654012621134438, 0.5153614801189699, 0.5841324634911348], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68eb1950&gt;: [0.5617404550719414, 0.5797617366895044, 0.5849153300422236, 0.649383981320446, 0.5687686935620206, 0.5300797124561587, 0.5719300277183739, 0.5221612406404279, 0.5132591195001368, 0.5129018575978641, 0.5088216106653501, 0.5746106057171697, 0.5701750808248407, 0.5546590874625247, 0.6340343646611318, 0.5566055623645138, 0.5283067350687806, 0.5378249211367877, 0.5597943194537027, 0.5352817530204381], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68d98ad0&gt;: [0.5963706984430727, 0.6425608340635431, 0.592364156949401, 0.6440983217626362, 0.6024030732666792, 0.522003936211167, 0.49176586183641646, 0.5767500212020209, 0.5773546027937172, 0.5839605654409954, 0.5384843786414345, 0.6148520542858776, 0.6857486067994942, 0.6232869191085517, 0.5786564421400543, 0.576158490493749, 0.5749552698193331, 0.5838580356867715, 0.5957714915802664, 0.5812780150010267], &lt;method-wrapper \'__str__\' of SVC object at 0x7f9e68d99010&gt;: [0.5761654006371805, 0.6077717512342676, 0.5599332758435563, 0.6484701889895875, 0.5835715630692735, 0.5293653037379075, 0.5161346037611836, 0.521540882041652, 0.5149514699066777, 0.5387405947211019, 0.5082904284712835, 0.5913399407278082, 0.5812873957277483, 0.5556683486230711, 0.6346564599782595, 0.5561325407026372, 0.5002497203563346, 0.5384197809222662, 0.5608743779769996, 0.5479004355064556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68d98d50&gt;: [12.515157426776788, 14.016976317990006, 11.013338535563573, 10.512732238492502, 13.516370020918933, 15.018188912132148, 9.010913347279288, 11.513944832634646, 9.010913347279288, 11.513944832634646, 14.016976317990004, 10.01212594142143, 10.512732238492504, 12.014551129705717, 10.512732238492502, 8.510307050208217, 9.51151964435036, 12.515157426776788, 10.01212594142143, 8.510307050208217], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68d98bd0&gt;: [2.8558011618609314, 2.9553433545958234, 4.818082297952214, 2.8349111980168167, 2.8661520393845277, 2.3986106679733172, 1.8144445155257864, 1.4222836220148969, 2.881410543393807, 4.786653247787582, 1.9590383869393624, 2.8220124028519176, 4.3231074607159785, 2.922466637732884, 2.3312213587522113, 1.8891011600769554, 1.861855903048851, 2.3671816178086837, 2.887954045374718, 2.3246778567713013], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f9e68d98c90&gt;: [0.4405340671158457, 1.0793632686195638, 2.4417759439617277, 0.5075446129877584, 0.9357889334089252, 0.5230250191431924, 0.4146871096398733, 0.49707056761035656, 1.018107350436292, 1.9829339007819442, 0.5521280538126783, 1.4479875463526861, 1.9468504738716668, 0.9518363117104739, 0.9445689763804105, 0.9389531903425166, 1.4275570605978223, 0.4332173646396078, 1.4380961469183409, 0.41086406030024525]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbf0680290&gt;: [0.9290268022046315, 0.461772373882692, 0.5235978750777759, 0.48738436628126536, 0.5655776811831355, 0.5100281517430181, 0.48474406427969696, 0.9963730942116461, 0.9804096056161973, 0.9934495881871926, 0.43319861383335423, 0.9813893975278156, 0.5330980123320286, 0.4220626010838741, 0.5234163792800152, 0.9605540225612701, 0.46873448146084495, 0.4321543450789637, 0.5361237906819508, 0.49914343132219585], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb451210&gt;: [0.4483419490536529, 0.4638514112820818, 0.4763438669359381, 0.44602732392609074, 0.5187564194216966, 0.49751353197518494, 0.4694355062725653, 0.45233616635848367, 0.45389875055809514, 0.4804743448647037, 0.44345030374394717, 0.4793193540860366, 0.5002707786067143, 0.43219926484033144, 0.4548611047346937, 0.4875211327717283, 0.4359213185203364, 0.4529468627358533, 0.497711678716965, 0.4731981369023405], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fdbfb30a850&gt;: [0.4409322699647559, 0.45410161095103013, 0.4675693066885219, 0.45871696783941057, 0.5034527964119152, 0.49616264350499545, 0.4693029607694249, 0.46674957573938475, 0.4479727590522069, 0.4744571077100732, 0.43914199540322635, 0.4902653891109245, 0.4978444927926264, 0.44974219683591915, 0.44761170637993203, 0.49759969619861555, 0.4323819792311829, 0.4630937001407474, 0.5034225673430281, 0.45121337312068543], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb448dd0&gt;: [4.772324692072311, 7.569849457361083, 7.491552895084613, 1.5978431919807856, 0.9617864500922033, 0.8205980754654508, 0.5468471157030775, 10.550791005753759, 2.230191863288911, 2.9261338404552597, 0.4390486228885994, 1.3416190736211935, 0.7623105884186407, 6.618061898078216, 0.3802151430839021, 2.3367302979896496, 1.1285123328681022, 0.8284114256736219, 1.0153231069129338, 0.6369681732680568], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbf56f9c90&gt;: [0.9892416051735986, 0.6780760155701049, 2.314978446197939, 0.41739350842118306, 4.277450327974198, 0.5764659025216805, 0.41949096717944506, 2.855065914607064, 0.42974007754710036, 0.6323660126134217, 0.40928578406510446, 0.5985655199505096, 0.6002018074544583, 0.33499860940428694, 0.3024825351832896, 2.021265737865705, 0.5863422878895774, 1.233946031876152, 0.9177625437092944, 0.4663113548957542], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fdbfb2f9250&gt;: [0.32796601443561646, 0.5497778864005797, 0.7096815148414121, 0.3072522536697413, 2.6123298587489217, 0.751672362734369, 0.44058492210954747, 0.41832028567671364, 0.4599606796021163, 1.9985923724834522, 0.34332719547053636, 0.6653136605515492, 0.6515793429699855, 0.3855709846241933, 1.7776804074658497, 0.6944652494643706, 0.4951756081384754, 0.5959198323906187, 0.7489486876937429, 0.472098132086715], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdbfb2f2c10&gt;: [0.511216117989339, 0.5303955205054371, 0.5671954561935144, 0.529261810986315, 0.5762478223094354, 0.6122443796585946, 0.532461829456329, 0.5165671481794416, 0.522315142564437, 0.5173628194744208, 0.5191522813645661, 0.5817142227448556, 0.5872013231691936, 0.502117291674917, 0.4449328463633581, 0.5645606769913156, 0.5582487034330698, 0.5450584104063356, 0.6073994959749096, 0.49305558023403695], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc04084ad0&gt;: [0.5448904272647798, 0.5792337179748118, 0.539684129879009, 0.5364384049496979, 0.5856828206549193, 0.6238814566275345, 0.5668535297548507, 0.5901125550591168, 0.5232388944266165, 0.5927001016475928, 0.5347637893119739, 0.612609860731571, 0.6026291150333383, 0.5481570746225355, 0.49084744611100883, 0.5972572759676797, 0.591580373096467, 0.5647013726569011, 0.6400752988580031, 0.5652123729431834], &lt;method-wrapper \'__str__\' of SVC object at 0x7fdc04087a50&gt;: [0.5126160004224274, 0.53005073127191, 0.5521430666139394, 0.5299976882478747, 0.5771999357498159, 0.6517622558139755, 0.5324942556752897, 0.5156936353691903, 0.5358210276873725, 0.5035883664377732, 0.5173304655594675, 0.5543568373346128, 0.6004555083754562, 0.47564517107712195, 0.44425164865918604, 0.5930017090000261, 0.5680679233201479, 0.545469713689622, 0.6078688622539636, 0.5071012270291363], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040853d0&gt;: [10.01212594142143, 11.013338535563573, 8.510307050208217, 9.511519644350361, 7.509094456066074, 10.512732238492502, 7.008488158995003, 11.013338535563573, 8.510307050208219, 9.511519644350361, 9.010913347279288, 9.010913347279288, 12.014551129705715, 10.01212594142143, 8.510307050208217, 10.512732238492504, 10.01212594142143, 10.01212594142143, 9.51151964435036, 9.010913347279288], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc04087050&gt;: [2.3704533687991387, 2.374448953138747, 1.3997577826755545, 1.3628854814730071, 2.388071581652799, 4.826797299980584, 1.889101160076955, 1.4624276742078992, 1.4431735858590118, 2.8429023666960322, 1.3805036943266673, 1.3837754453171223, 4.789924998778037, 2.400970376817698, 0.8951559012648749, 2.3969747924780895, 3.335517495087888, 2.3760848286339744, 3.7758136094709958, 0.9256729092834335], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fdc040877d0&gt;: [0.465025178153434, 1.4378585709752443, 0.4813525855118262, 0.9294986811680528, 0.9659765452244654, 1.9682580427157212, 1.4146088982867486, 1.0174328842333138, 0.47578616662010703, 0.9552805977009089, 1.4486195594419171, 0.477908299521391, 1.4283883880038388, 0.583664598034175, 0.44668313195062115, 1.0217735385728817, 0.4733614168326101, 0.49447328282287967, 2.4141205759905477, 0.4888574967849857]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d36701c10&gt;: [1.006277556577236, 0.5513912554890108, 0.9297631343846846, 0.5151420065779138, 0.9536936232082418, 0.4874247726296594, 0.47353404978931984, 0.49907895447942363, 0.5342854259038959, 0.5323652181850949, 0.9799443416952069, 0.5542627835015921, 0.6065692986794402, 0.5073721759445083, 0.5205573500983339, 0.9697965175547818, 0.5295985733636797, 0.9987946690331015, 0.49452218382544, 0.5127750206340284], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d36b4af10&gt;: [0.4992081336039442, 0.5419938646663974, 0.46159871096962163, 0.43856179579662563, 0.4813397658728255, 0.4443520532295378, 0.49181297598106016, 0.48174097750525413, 0.50370074995251, 0.48888964632713006, 0.4721159918873842, 0.535800690401881, 0.5973569231532793, 0.5098053926302717, 0.489909709457647, 0.4855258381849637, 0.5028156072570376, 0.4890322929533706, 0.488717984191686, 0.4707168731629701], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1d3671fad0&gt;: [0.47243446523436256, 0.5320019494017749, 0.47379825611543097, 0.4441693106220262, 0.49617077855851277, 0.445436939417135, 0.5032507502026696, 0.47260711148235884, 0.49325819479600086, 0.49532152133416063, 0.46020218908643784, 0.5212093394017044, 0.5732251985927347, 0.5094206116143422, 0.4857108139964513, 0.48049368605962667, 0.4973918755169033, 0.4882668827723837, 0.47796510305291207, 0.4738288223283674], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d390ab9d0&gt;: [0.7201057306378938, 13.313820399922356, 11.626402008793836, 0.5295915557664477, 6.208795097359145, 1.6681079993966312, 2.0940445348711276, 0.5546538728653645, 12.297151236871834, 3.7828327516963123, 6.323922172156113, 1.9002270686453135, 5.114957289796096, 3.424826045318669, 9.807788379033632, 7.275259482945633, 1.1589137006977905, 8.338540058328688, 12.712466743955652, 4.730640059077718], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d362c0a50&gt;: [3.4604217318251838, 0.5976849644298697, 0.47504842625900057, 0.5735544218942041, 0.7051272484648394, 0.4456506738137245, 0.431594126858453, 0.8462415011134059, 0.8686010323759176, 0.7235365751894626, 0.445576338210265, 0.849355801947283, 1.1437454822631765, 1.0211698587962676, 0.631551259647567, 0.4208871367120596, 3.89819765299683, 0.7466792791839553, 0.6470191676820161, 1.096257973087252], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1d35b043d0&gt;: [3.4592852018883216, 0.5784831220598132, 1.5883091049711626, 0.6267809635783349, 4.383150364831179, 0.4204194039231516, 0.5639133760953422, 0.4510912307281177, 0.7160943325927926, 0.8451894162348551, 0.9860372012614513, 0.648004644800067, 0.7165389577580457, 0.7321058659790024, 0.5324198479088997, 0.4638697945147245, 0.5824157705477349, 0.9148191147080169, 1.787043132898794, 0.40924378585875804], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d3666bc50&gt;: [0.5711902275539885, 0.5289453498082609, 0.5451805172813293, 0.5922851032140449, 0.605315490192052, 0.5322741997689779, 0.5205112379172105, 0.5756310715151784, 0.5884144336741496, 0.6341997135304859, 0.4592849959022946, 0.5962344205703656, 0.6315242212763623, 0.6344477063383329, 0.5614635712287317, 0.550896914865098, 0.5782793314499185, 0.5789234550299116, 0.5928757088410722, 0.5517071734896033], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d36b0ef10&gt;: [0.5937810428154788, 0.6042235552797236, 0.5503224106004554, 0.5818758035650631, 0.5714260761698694, 0.5765339208293802, 0.6004118427988221, 0.6229032822136297, 0.6113371920371016, 0.6301914883128354, 0.49214501921062337, 0.5878697786603166, 0.6912377956710594, 0.656800686121827, 0.5523250162189075, 0.5909003638516989, 0.6297967917827401, 0.6321804334384046, 0.5706540085270915, 0.6226252479538796], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1d36b0f010&gt;: [0.5300567588920675, 0.5440398146334174, 0.5314868752225964, 0.6061664690202662, 0.6053280747224551, 0.4898224358057928, 0.5202841452360111, 0.5625539832106381, 0.6039156959438936, 0.6499074747276392, 0.47409539690546065, 0.5958540893455226, 0.6597133379858632, 0.6348469002966954, 0.5610225564108741, 0.5239143979978831, 0.5361992393105162, 0.5961503576193269, 0.6195861734589568, 0.5515532935023697], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d35aad690&gt;: [11.513944832634646, 10.512732238492504, 6.507881861923931, 9.010913347279288, 14.016976317990006, 9.010913347279288, 11.513944832634646, 13.015763723847861, 8.009700753137146, 10.512732238492504, 10.512732238492504, 10.01212594142143, 8.009700753137146, 14.517582615061075, 12.014551129705717, 11.013338535563573, 10.01212594142143, 12.515157426776788, 10.01212594142143, 11.513944832634646], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d35aad450&gt;: [2.3070596439176416, 0.5013591322587584, 2.8943093385587058, 1.9109031660671443, 3.9469289045635225, 1.4302747906941131, 4.419377902460416, 5.325043888207275, 1.8465973990395719, 3.390920051290169, 2.3953389169828623, 2.4218603406618127, 2.9112037180632124, 4.8549545991547625, 3.371665962941282, 1.4736905938775704, 2.8790508345494263, 4.833340801961494, 1.4190118710244417, 1.4584320898682914], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1d4b469950&gt;: [0.877509063362323, 0.549373907822163, 0.5022919165021159, 0.5059581046387057, 2.0271385782576714, 0.4354045384840084, 0.577703741996321, 1.5627882430968576, 0.4579303778233508, 1.5510884331673043, 0.9736226439037217, 0.9703508929132667, 1.0442837041152826, 1.5374007637101361, 0.5044297232003417, 0.5117464256765796, 1.9609907073856583, 1.0448506762613972, 0.4955421861719926, 0.5439149829873073]}'}</t>
-  </si>
-  <si>
-    <t>{0: 'SVC(random_state=13)WITHOUT log_loss_field', 1: 'SVC(random_state=13)WITHOUT log_loss_field', 2: 'SVC(random_state=13)WITHOUT log_loss_field', 3: 'SVC(random_state=13)WITHOUT log_loss_field', 4: 'SVC(random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
@@ -692,47 +668,41 @@
       <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
       <c r="F2">
-        <v>0.9454626392126393</v>
+        <v>0.9671296296296296</v>
       </c>
       <c r="G2">
-        <v>0.01429508583773754</v>
+        <v>0.02685185185185184</v>
       </c>
       <c r="H2">
-        <v>0.8333333333333334</v>
+        <v>0.8777777777777777</v>
       </c>
       <c r="I2">
-        <v>0.04648111258522641</v>
+        <v>0.05443310539518172</v>
       </c>
       <c r="J2">
-        <v>0.8325563325563327</v>
+        <v>0.8777777777777779</v>
       </c>
       <c r="K2">
-        <v>0.05227272366347048</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="L2">
-        <v>0.8368279868279869</v>
+        <v>0.8992063492063492</v>
       </c>
       <c r="M2">
-        <v>0.04366599869208283</v>
+        <v>0.05456024521364197</v>
       </c>
       <c r="N2">
-        <v>0.8325563325563327</v>
+        <v>0.8777777777777779</v>
       </c>
       <c r="O2">
-        <v>0.05227272366347048</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="P2">
-        <v>0.8294612276085201</v>
+        <v>0.8765723165723166</v>
       </c>
       <c r="Q2">
-        <v>0.05526733744643951</v>
+        <v>0.05255965485897219</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
@@ -740,49 +710,49 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
       </c>
       <c r="F3">
-        <v>0.9454108391608391</v>
+        <v>0.9648148148148149</v>
       </c>
       <c r="G3">
-        <v>0.01259526033696217</v>
+        <v>0.02082818866518887</v>
       </c>
       <c r="H3">
-        <v>0.8333333333333334</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I3">
-        <v>0.04648111258522641</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J3">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K3">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L3">
-        <v>0.8368279868279869</v>
+        <v>0.8703968253968254</v>
       </c>
       <c r="M3">
-        <v>0.04366599869208283</v>
+        <v>0.04871464517030822</v>
       </c>
       <c r="N3">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O3">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P3">
-        <v>0.8294612276085201</v>
+        <v>0.8394494394494394</v>
       </c>
       <c r="Q3">
-        <v>0.05526733744643951</v>
+        <v>0.04302908157079199</v>
       </c>
       <c r="R3" t="s">
         <v>50</v>
@@ -790,446 +760,452 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="F4">
-        <v>0.9454108391608391</v>
+        <v>0.9638888888888889</v>
       </c>
       <c r="G4">
-        <v>0.01259526033696217</v>
+        <v>0.02078698548207744</v>
       </c>
       <c r="H4">
-        <v>0.8333333333333334</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I4">
-        <v>0.04648111258522641</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J4">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K4">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L4">
-        <v>0.8368279868279869</v>
+        <v>0.8703968253968254</v>
       </c>
       <c r="M4">
-        <v>0.04366599869208283</v>
+        <v>0.04871464517030822</v>
       </c>
       <c r="N4">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O4">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P4">
-        <v>0.8294612276085201</v>
+        <v>0.8394494394494394</v>
       </c>
       <c r="Q4">
-        <v>0.05526733744643951</v>
+        <v>0.04302908157079199</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>48</v>
       </c>
       <c r="F5">
-        <v>0.9451793576793577</v>
+        <v>0.9638888888888889</v>
       </c>
       <c r="G5">
-        <v>0.01229897439552958</v>
+        <v>0.02078698548207744</v>
       </c>
       <c r="H5">
-        <v>0.8333333333333334</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I5">
-        <v>0.04648111258522641</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J5">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K5">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L5">
-        <v>0.8368279868279869</v>
+        <v>0.8703968253968254</v>
       </c>
       <c r="M5">
-        <v>0.04366599869208283</v>
+        <v>0.04871464517030822</v>
       </c>
       <c r="N5">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O5">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P5">
-        <v>0.8294612276085201</v>
+        <v>0.8394494394494394</v>
       </c>
       <c r="Q5">
-        <v>0.05526733744643951</v>
+        <v>0.04302908157079199</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
       </c>
       <c r="F6">
-        <v>0.944766576016576</v>
+        <v>0.9638888888888889</v>
       </c>
       <c r="G6">
-        <v>0.01398864458471371</v>
+        <v>0.02078698548207744</v>
       </c>
       <c r="H6">
-        <v>0.8333333333333334</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I6">
-        <v>0.04648111258522641</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J6">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K6">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L6">
-        <v>0.8368279868279869</v>
+        <v>0.8703968253968254</v>
       </c>
       <c r="M6">
-        <v>0.04366599869208283</v>
+        <v>0.04871464517030822</v>
       </c>
       <c r="N6">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O6">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P6">
-        <v>0.8294612276085201</v>
+        <v>0.8394494394494394</v>
       </c>
       <c r="Q6">
-        <v>0.05526733744643951</v>
+        <v>0.04302908157079199</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
       </c>
       <c r="F7">
-        <v>0.9443036130536131</v>
+        <v>0.962962962962963</v>
       </c>
       <c r="G7">
-        <v>0.01336485451400523</v>
+        <v>0.01920040866048861</v>
       </c>
       <c r="H7">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I7">
-        <v>0.04648111258522641</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J7">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K7">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L7">
-        <v>0.8368279868279869</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M7">
-        <v>0.04366599869208283</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N7">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O7">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P7">
-        <v>0.8294612276085201</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q7">
-        <v>0.05526733744643951</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
       </c>
       <c r="F8">
-        <v>0.9443036130536131</v>
+        <v>0.962962962962963</v>
       </c>
       <c r="G8">
-        <v>0.01336485451400523</v>
+        <v>0.02131641561707654</v>
       </c>
       <c r="H8">
-        <v>0.8333333333333334</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I8">
-        <v>0.04648111258522641</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J8">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K8">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L8">
-        <v>0.8368279868279869</v>
+        <v>0.8703968253968254</v>
       </c>
       <c r="M8">
-        <v>0.04366599869208283</v>
+        <v>0.04871464517030822</v>
       </c>
       <c r="N8">
-        <v>0.8325563325563327</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O8">
-        <v>0.05227272366347048</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P8">
-        <v>0.8294612276085201</v>
+        <v>0.8394494394494394</v>
       </c>
       <c r="Q8">
-        <v>0.05526733744643951</v>
+        <v>0.04302908157079199</v>
       </c>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
       </c>
       <c r="F9">
-        <v>0.9438746438746438</v>
+        <v>0.962037037037037</v>
       </c>
       <c r="G9">
-        <v>0.01389966280363694</v>
+        <v>0.01906598174256852</v>
       </c>
       <c r="H9">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I9">
-        <v>0.04648111258522641</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J9">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K9">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L9">
-        <v>0.8368279868279869</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M9">
-        <v>0.04366599869208283</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N9">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O9">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P9">
-        <v>0.8294612276085201</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q9">
-        <v>0.05526733744643951</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
       </c>
       <c r="F10">
-        <v>0.9436431623931624</v>
+        <v>0.962037037037037</v>
       </c>
       <c r="G10">
-        <v>0.01368638746394105</v>
+        <v>0.01906598174256852</v>
       </c>
       <c r="H10">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I10">
-        <v>0.04648111258522641</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J10">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K10">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L10">
-        <v>0.8368279868279869</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M10">
-        <v>0.04366599869208283</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N10">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O10">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P10">
-        <v>0.8294612276085201</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q10">
-        <v>0.05526733744643951</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
       </c>
       <c r="F11">
-        <v>0.9434489121989124</v>
+        <v>0.962037037037037</v>
       </c>
       <c r="G11">
-        <v>0.01257957493983936</v>
+        <v>0.01951046991269024</v>
       </c>
       <c r="H11">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I11">
-        <v>0.04648111258522641</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J11">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K11">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L11">
-        <v>0.8368279868279869</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M11">
-        <v>0.04366599869208283</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N11">
-        <v>0.8325563325563327</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O11">
-        <v>0.05227272366347048</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P11">
-        <v>0.8294612276085201</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q11">
-        <v>0.05526733744643951</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
       </c>
       <c r="F12">
-        <v>0.9404428904428904</v>
+        <v>0.962037037037037</v>
       </c>
       <c r="G12">
-        <v>0.00878778733008324</v>
+        <v>0.01906598174256852</v>
       </c>
       <c r="H12">
-        <v>0.8166666666666668</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I12">
-        <v>0.02222222222222223</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J12">
-        <v>0.8168220668220668</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K12">
-        <v>0.0279480061749728</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L12">
-        <v>0.8197772815419875</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M12">
-        <v>0.01989148328240349</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N12">
-        <v>0.8168220668220668</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O12">
-        <v>0.0279480061749728</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P12">
-        <v>0.8151198045111089</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q12">
-        <v>0.02874372188698949</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R12" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1237,49 +1213,49 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="F13">
-        <v>0.9400770525770525</v>
+        <v>0.962037037037037</v>
       </c>
       <c r="G13">
-        <v>0.02328712111276809</v>
+        <v>0.01951046991269024</v>
       </c>
       <c r="H13">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I13">
-        <v>0.04444444444444447</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J13">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K13">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L13">
-        <v>0.8416342916342916</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M13">
-        <v>0.04121798915556851</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N13">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O13">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P13">
-        <v>0.8347081599569017</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q13">
-        <v>0.05398368698928416</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1287,49 +1263,49 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
       </c>
       <c r="F14">
-        <v>0.9400770525770525</v>
+        <v>0.961111111111111</v>
       </c>
       <c r="G14">
-        <v>0.02328712111276809</v>
+        <v>0.0197723671333913</v>
       </c>
       <c r="H14">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I14">
-        <v>0.04444444444444447</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J14">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K14">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L14">
-        <v>0.8416342916342916</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M14">
-        <v>0.04121798915556851</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N14">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O14">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P14">
-        <v>0.8347081599569017</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q14">
-        <v>0.05398368698928416</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R14" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1337,49 +1313,49 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="F15">
-        <v>0.9400770525770525</v>
+        <v>0.961111111111111</v>
       </c>
       <c r="G15">
-        <v>0.02328712111276809</v>
+        <v>0.0197723671333913</v>
       </c>
       <c r="H15">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I15">
-        <v>0.04444444444444447</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J15">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K15">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L15">
-        <v>0.8416342916342916</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M15">
-        <v>0.04121798915556851</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N15">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O15">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P15">
-        <v>0.8347081599569017</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q15">
-        <v>0.05398368698928416</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1387,49 +1363,49 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
         <v>48</v>
       </c>
       <c r="F16">
-        <v>0.9391236078736078</v>
+        <v>0.961111111111111</v>
       </c>
       <c r="G16">
-        <v>0.02303284789965826</v>
+        <v>0.0197723671333913</v>
       </c>
       <c r="H16">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I16">
-        <v>0.04779069592801459</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J16">
-        <v>0.8390442890442891</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K16">
-        <v>0.05448994601062163</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L16">
-        <v>0.8434324934324934</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M16">
-        <v>0.04644099274153663</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N16">
-        <v>0.8390442890442891</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O16">
-        <v>0.05448994601062163</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P16">
-        <v>0.8351763873816509</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q16">
-        <v>0.05742443270157538</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R16" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1437,404 +1413,398 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="F17">
-        <v>0.938992488992489</v>
+        <v>0.961111111111111</v>
       </c>
       <c r="G17">
-        <v>0.02089129106070035</v>
+        <v>0.0197723671333913</v>
       </c>
       <c r="H17">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="I17">
-        <v>0.04444444444444447</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J17">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K17">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L17">
-        <v>0.8416342916342916</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M17">
-        <v>0.04121798915556851</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N17">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O17">
-        <v>0.0510589730204187</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P17">
-        <v>0.8347081599569017</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q17">
-        <v>0.05398368698928416</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R17" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="F18">
-        <v>0.9383498445998446</v>
+        <v>0.961111111111111</v>
       </c>
       <c r="G18">
-        <v>0.02108000610959418</v>
+        <v>0.02163578045471835</v>
       </c>
       <c r="H18">
-        <v>0.8388888888888889</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="I18">
-        <v>0.04444444444444447</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="J18">
-        <v>0.8386169386169385</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="K18">
-        <v>0.0510589730204187</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="L18">
-        <v>0.8416342916342916</v>
+        <v>0.8796825396825396</v>
       </c>
       <c r="M18">
-        <v>0.04121798915556851</v>
+        <v>0.03543844090783806</v>
       </c>
       <c r="N18">
-        <v>0.8386169386169385</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="O18">
-        <v>0.0510589730204187</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="P18">
-        <v>0.8347081599569017</v>
+        <v>0.8515972915972917</v>
       </c>
       <c r="Q18">
-        <v>0.05398368698928416</v>
+        <v>0.02809213791575926</v>
       </c>
       <c r="R18" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>0.9373575498575498</v>
+        <v>0.9597222222222224</v>
       </c>
       <c r="G19">
-        <v>0.02318202070348122</v>
+        <v>0.0246546795475821</v>
       </c>
       <c r="H19">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I19">
-        <v>0.04648111258522641</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J19">
-        <v>0.8334887334887334</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="K19">
-        <v>0.05291446601538775</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="L19">
-        <v>0.8381910681910683</v>
+        <v>0.883095238095238</v>
       </c>
       <c r="M19">
-        <v>0.04571081751803601</v>
+        <v>0.05905721888169826</v>
       </c>
       <c r="N19">
-        <v>0.8334887334887334</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="O19">
-        <v>0.05291446601538775</v>
+        <v>0.05665577237325317</v>
       </c>
       <c r="P19">
-        <v>0.8293980540670857</v>
+        <v>0.8638161838161839</v>
       </c>
       <c r="Q19">
-        <v>0.05589174871774832</v>
+        <v>0.05819718539853101</v>
       </c>
       <c r="R19" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="F20">
-        <v>0.937338124838125</v>
+        <v>0.9592592592592594</v>
       </c>
       <c r="G20">
-        <v>0.0242770997015742</v>
+        <v>0.02139670371905802</v>
       </c>
       <c r="H20">
-        <v>0.8166666666666668</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="I20">
-        <v>0.04513354669242203</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="J20">
-        <v>0.8168220668220668</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="K20">
-        <v>0.05015448231107242</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="L20">
-        <v>0.8221607096607096</v>
+        <v>0.8796825396825396</v>
       </c>
       <c r="M20">
-        <v>0.04302537343782498</v>
+        <v>0.03543844090783806</v>
       </c>
       <c r="N20">
-        <v>0.8168220668220668</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="O20">
-        <v>0.05015448231107242</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="P20">
-        <v>0.8118677852724492</v>
+        <v>0.8515972915972917</v>
       </c>
       <c r="Q20">
-        <v>0.0542610830296473</v>
+        <v>0.02809213791575926</v>
       </c>
       <c r="R20" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="F21">
-        <v>0.9368006993006993</v>
+        <v>0.9592592592592594</v>
       </c>
       <c r="G21">
-        <v>0.01977996419645272</v>
+        <v>0.02139670371905802</v>
       </c>
       <c r="H21">
-        <v>0.8388888888888889</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I21">
-        <v>0.04444444444444447</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J21">
-        <v>0.8386169386169385</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K21">
-        <v>0.0510589730204187</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L21">
-        <v>0.8416342916342916</v>
+        <v>0.8703968253968254</v>
       </c>
       <c r="M21">
-        <v>0.04121798915556851</v>
+        <v>0.04871464517030822</v>
       </c>
       <c r="N21">
-        <v>0.8386169386169385</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O21">
-        <v>0.0510589730204187</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P21">
-        <v>0.8347081599569017</v>
+        <v>0.8394494394494394</v>
       </c>
       <c r="Q21">
-        <v>0.05398368698928416</v>
+        <v>0.04302908157079199</v>
       </c>
       <c r="R21" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="F22">
-        <v>0.9357048044548044</v>
+        <v>0.9592592592592594</v>
       </c>
       <c r="G22">
-        <v>0.02346083499052014</v>
+        <v>0.02139670371905802</v>
       </c>
       <c r="H22">
-        <v>0.8111111111111111</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="I22">
-        <v>0.04082482904638632</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="J22">
-        <v>0.8112665112665113</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="K22">
-        <v>0.04555878974127352</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="L22">
-        <v>0.8166051541051541</v>
+        <v>0.8652380952380951</v>
       </c>
       <c r="M22">
-        <v>0.03834882318956981</v>
+        <v>0.02871393034605966</v>
       </c>
       <c r="N22">
-        <v>0.8112665112665113</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="O22">
-        <v>0.04555878974127352</v>
+        <v>0.04157397096415488</v>
       </c>
       <c r="P22">
-        <v>0.8064831698878339</v>
+        <v>0.8100099900099899</v>
       </c>
       <c r="Q22">
-        <v>0.04970009721601346</v>
+        <v>0.0527550530817008</v>
       </c>
       <c r="R22" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="F23">
-        <v>0.9343466718466719</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G23">
-        <v>0.02250639601308296</v>
+        <v>0.0211143597240581</v>
       </c>
       <c r="H23">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I23">
-        <v>0.03239417719358502</v>
+        <v>0.04444444444444441</v>
       </c>
       <c r="J23">
-        <v>0.839121989121989</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K23">
-        <v>0.03798798835076787</v>
+        <v>0.04444444444444447</v>
       </c>
       <c r="L23">
-        <v>0.8438643056290115</v>
+        <v>0.8711111111111112</v>
       </c>
       <c r="M23">
-        <v>0.0296700262529276</v>
+        <v>0.04514638434192047</v>
       </c>
       <c r="N23">
-        <v>0.839121989121989</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O23">
-        <v>0.03798798835076787</v>
+        <v>0.04444444444444447</v>
       </c>
       <c r="P23">
-        <v>0.8375535736405301</v>
+        <v>0.8658896658896659</v>
       </c>
       <c r="Q23">
-        <v>0.03884629832694857</v>
+        <v>0.04483395478791714</v>
       </c>
       <c r="R23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="F24">
-        <v>0.9341135716135716</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G24">
-        <v>0.022925817241064</v>
+        <v>0.0211143597240581</v>
       </c>
       <c r="H24">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I24">
-        <v>0.03239417719358502</v>
+        <v>0.04444444444444441</v>
       </c>
       <c r="J24">
-        <v>0.839121989121989</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K24">
-        <v>0.03798798835076787</v>
+        <v>0.04444444444444447</v>
       </c>
       <c r="L24">
-        <v>0.8438643056290115</v>
+        <v>0.8711111111111112</v>
       </c>
       <c r="M24">
-        <v>0.0296700262529276</v>
+        <v>0.04514638434192047</v>
       </c>
       <c r="N24">
-        <v>0.839121989121989</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O24">
-        <v>0.03798798835076787</v>
+        <v>0.04444444444444447</v>
       </c>
       <c r="P24">
-        <v>0.8375535736405301</v>
+        <v>0.8658896658896659</v>
       </c>
       <c r="Q24">
-        <v>0.03884629832694857</v>
+        <v>0.04483395478791714</v>
       </c>
       <c r="R24" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
@@ -1843,142 +1813,148 @@
         <v>48</v>
       </c>
       <c r="F25">
-        <v>0.9338820901320901</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G25">
-        <v>0.0227082859712723</v>
+        <v>0.0211143597240581</v>
       </c>
       <c r="H25">
-        <v>0.8444444444444444</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I25">
-        <v>0.03333333333333335</v>
+        <v>0.04444444444444441</v>
       </c>
       <c r="J25">
-        <v>0.8446775446775447</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K25">
-        <v>0.03895297164339946</v>
+        <v>0.04444444444444447</v>
       </c>
       <c r="L25">
-        <v>0.8477104594751653</v>
+        <v>0.8711111111111112</v>
       </c>
       <c r="M25">
-        <v>0.03040099991574946</v>
+        <v>0.04514638434192047</v>
       </c>
       <c r="N25">
-        <v>0.8446775446775447</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O25">
-        <v>0.03895297164339946</v>
+        <v>0.04444444444444447</v>
       </c>
       <c r="P25">
-        <v>0.8426260374086461</v>
+        <v>0.8658896658896659</v>
       </c>
       <c r="Q25">
-        <v>0.03988978072910207</v>
+        <v>0.04483395478791714</v>
       </c>
       <c r="R25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="F26">
-        <v>0.9327052577052577</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G26">
-        <v>0.02150325766197343</v>
+        <v>0.02151657414559674</v>
       </c>
       <c r="H26">
-        <v>0.8444444444444444</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="I26">
-        <v>0.03333333333333335</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="J26">
-        <v>0.8446775446775447</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="K26">
-        <v>0.03895297164339946</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="L26">
-        <v>0.8477104594751653</v>
+        <v>0.8796825396825396</v>
       </c>
       <c r="M26">
-        <v>0.03040099991574946</v>
+        <v>0.03543844090783806</v>
       </c>
       <c r="N26">
-        <v>0.8446775446775447</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="O26">
-        <v>0.03895297164339946</v>
+        <v>0.02721655269759083</v>
       </c>
       <c r="P26">
-        <v>0.8426260374086461</v>
+        <v>0.8515972915972917</v>
       </c>
       <c r="Q26">
-        <v>0.03988978072910207</v>
+        <v>0.02809213791575926</v>
       </c>
       <c r="R26" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
         <v>22</v>
       </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>48</v>
+      </c>
       <c r="F27">
-        <v>0.9326906889406889</v>
+        <v>0.9574074074074075</v>
       </c>
       <c r="G27">
-        <v>0.02127540740410451</v>
+        <v>0.02139670371905803</v>
       </c>
       <c r="H27">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I27">
-        <v>0.03685138655950443</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="J27">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K27">
-        <v>0.04163509924001917</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="L27">
-        <v>0.8420772038419096</v>
+        <v>0.8745238095238095</v>
       </c>
       <c r="M27">
-        <v>0.03385775349093004</v>
+        <v>0.06579187965525406</v>
       </c>
       <c r="N27">
-        <v>0.8386169386169385</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O27">
-        <v>0.04163509924001917</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="P27">
-        <v>0.8371391281826064</v>
+        <v>0.8647752247752247</v>
       </c>
       <c r="Q27">
-        <v>0.04215661491416067</v>
+        <v>0.06842652511367502</v>
       </c>
       <c r="R27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
         <v>43</v>
@@ -1987,381 +1963,381 @@
         <v>48</v>
       </c>
       <c r="F28">
-        <v>0.932044807044807</v>
+        <v>0.9546296296296297</v>
       </c>
       <c r="G28">
-        <v>0.02126042518282869</v>
+        <v>0.02312962221629036</v>
       </c>
       <c r="H28">
-        <v>0.8388888888888889</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I28">
-        <v>0.03239417719358502</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="J28">
-        <v>0.839121989121989</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K28">
-        <v>0.03798798835076787</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="L28">
-        <v>0.8438643056290115</v>
+        <v>0.8745238095238095</v>
       </c>
       <c r="M28">
-        <v>0.0296700262529276</v>
+        <v>0.06579187965525406</v>
       </c>
       <c r="N28">
-        <v>0.839121989121989</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O28">
-        <v>0.03798798835076787</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="P28">
-        <v>0.8375535736405301</v>
+        <v>0.8647752247752247</v>
       </c>
       <c r="Q28">
-        <v>0.03884629832694857</v>
+        <v>0.06842652511367502</v>
       </c>
       <c r="R28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="F29">
-        <v>0.9313843563843565</v>
+        <v>0.9546296296296297</v>
       </c>
       <c r="G29">
-        <v>0.02122807543126962</v>
+        <v>0.02657907424890244</v>
       </c>
       <c r="H29">
-        <v>0.8444444444444444</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I29">
-        <v>0.03333333333333335</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="J29">
-        <v>0.8446775446775447</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="K29">
-        <v>0.03895297164339946</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="L29">
-        <v>0.8477104594751653</v>
+        <v>0.8745238095238095</v>
       </c>
       <c r="M29">
-        <v>0.03040099991574946</v>
+        <v>0.06579187965525406</v>
       </c>
       <c r="N29">
-        <v>0.8446775446775447</v>
+        <v>0.8666666666666668</v>
       </c>
       <c r="O29">
-        <v>0.03895297164339946</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="P29">
-        <v>0.8426260374086461</v>
+        <v>0.8647752247752247</v>
       </c>
       <c r="Q29">
-        <v>0.03988978072910207</v>
+        <v>0.06842652511367502</v>
       </c>
       <c r="R29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F30">
-        <v>0.9281533281533282</v>
+        <v>0.9527777777777778</v>
       </c>
       <c r="G30">
-        <v>0.0200822552859745</v>
+        <v>0.02099219268287893</v>
       </c>
       <c r="H30">
-        <v>0.8222222222222223</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="I30">
-        <v>0.03767961101736262</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J30">
-        <v>0.8223776223776224</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="K30">
-        <v>0.04465331595324425</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="L30">
-        <v>0.828017908017908</v>
+        <v>0.871984126984127</v>
       </c>
       <c r="M30">
-        <v>0.03636000135373591</v>
+        <v>0.05410091072425915</v>
       </c>
       <c r="N30">
-        <v>0.8223776223776224</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="O30">
-        <v>0.04465331595324425</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="P30">
-        <v>0.8193208419608882</v>
+        <v>0.8650860250860252</v>
       </c>
       <c r="Q30">
-        <v>0.04795636839774353</v>
+        <v>0.05869365690285176</v>
       </c>
       <c r="R30" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="F31">
-        <v>0.9274119399119399</v>
+        <v>0.950925925925926</v>
       </c>
       <c r="G31">
-        <v>0.01631595767050417</v>
+        <v>0.02709025710801445</v>
       </c>
       <c r="H31">
-        <v>0.8222222222222223</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I31">
-        <v>0.03767961101736262</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="J31">
-        <v>0.8223776223776224</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K31">
-        <v>0.04465331595324425</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="L31">
-        <v>0.828017908017908</v>
+        <v>0.8516402116402118</v>
       </c>
       <c r="M31">
-        <v>0.03636000135373591</v>
+        <v>0.06957267576314702</v>
       </c>
       <c r="N31">
-        <v>0.8223776223776224</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O31">
-        <v>0.04465331595324425</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="P31">
-        <v>0.8193208419608882</v>
+        <v>0.8401968401968402</v>
       </c>
       <c r="Q31">
-        <v>0.04795636839774353</v>
+        <v>0.079896101669404</v>
       </c>
       <c r="R31" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
         <v>48</v>
       </c>
       <c r="F32">
-        <v>0.9254985754985754</v>
+        <v>0.95</v>
       </c>
       <c r="G32">
-        <v>0.01648321479134056</v>
+        <v>0.02768503034764083</v>
       </c>
       <c r="H32">
-        <v>0.8</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="I32">
-        <v>0.04082482904638632</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="J32">
-        <v>0.8001554001554002</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="K32">
-        <v>0.0443039343009199</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="L32">
-        <v>0.8057956857956858</v>
+        <v>0.8618253968253968</v>
       </c>
       <c r="M32">
-        <v>0.04189658987112593</v>
+        <v>0.05473797498784293</v>
       </c>
       <c r="N32">
-        <v>0.8001554001554002</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="O32">
-        <v>0.0443039343009199</v>
+        <v>0.05665577237325319</v>
       </c>
       <c r="P32">
-        <v>0.7963171789572251</v>
+        <v>0.8537418137418136</v>
       </c>
       <c r="Q32">
-        <v>0.04886218573641389</v>
+        <v>0.05847786290181851</v>
       </c>
       <c r="R32" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>0.9236264892514893</v>
+        <v>0.9490740740740741</v>
       </c>
       <c r="G33">
-        <v>0.02068944491896048</v>
+        <v>0.02986021388258722</v>
       </c>
       <c r="H33">
-        <v>0.8111111111111111</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="I33">
-        <v>0.03685138655950446</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="J33">
-        <v>0.8121212121212121</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="K33">
-        <v>0.03787498237612985</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="L33">
-        <v>0.8138209013209015</v>
+        <v>0.7291678691678692</v>
       </c>
       <c r="M33">
-        <v>0.03795417656726954</v>
+        <v>0.1454089525381818</v>
       </c>
       <c r="N33">
-        <v>0.8121212121212121</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="O33">
-        <v>0.03787498237612985</v>
+        <v>0.05443310539518175</v>
       </c>
       <c r="P33">
-        <v>0.8108092957569799</v>
+        <v>0.7042042706748589</v>
       </c>
       <c r="Q33">
-        <v>0.0382248569225354</v>
+        <v>0.09550495021374142</v>
       </c>
       <c r="R33" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>0.9214128464128464</v>
+        <v>0.9481481481481483</v>
       </c>
       <c r="G34">
-        <v>0.01820272310965252</v>
+        <v>0.02977395405706206</v>
       </c>
       <c r="H34">
-        <v>0.7444444444444444</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="I34">
-        <v>0.0773799348732451</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="J34">
-        <v>0.7456487956487956</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K34">
-        <v>0.08410146004210681</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="L34">
-        <v>0.7419068649153452</v>
+        <v>0.8516402116402118</v>
       </c>
       <c r="M34">
-        <v>0.1339954407858886</v>
+        <v>0.06957267576314702</v>
       </c>
       <c r="N34">
-        <v>0.7456487956487956</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O34">
-        <v>0.08410146004210681</v>
+        <v>0.07370277311900887</v>
       </c>
       <c r="P34">
-        <v>0.7213338350249894</v>
+        <v>0.8401968401968402</v>
       </c>
       <c r="Q34">
-        <v>0.1076020638036043</v>
+        <v>0.079896101669404</v>
       </c>
       <c r="R34" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
         <v>48</v>
       </c>
       <c r="F35">
-        <v>0.9173756798756798</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G35">
-        <v>0.01410601523332799</v>
+        <v>0.03084876157214385</v>
       </c>
       <c r="H35">
-        <v>0.7833333333333334</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="I35">
-        <v>0.03685138655950446</v>
+        <v>0.07027283689263063</v>
       </c>
       <c r="J35">
-        <v>0.7824786324786326</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K35">
-        <v>0.04306722629401741</v>
+        <v>0.07027283689263066</v>
       </c>
       <c r="L35">
-        <v>0.7873055648055648</v>
+        <v>0.8398148148148149</v>
       </c>
       <c r="M35">
-        <v>0.04255494701602267</v>
+        <v>0.06222332450522758</v>
       </c>
       <c r="N35">
-        <v>0.7824786324786326</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="O35">
-        <v>0.04306722629401741</v>
+        <v>0.07027283689263066</v>
       </c>
       <c r="P35">
-        <v>0.7757269776729886</v>
+        <v>0.8283597883597883</v>
       </c>
       <c r="Q35">
-        <v>0.05181308016730775</v>
+        <v>0.07716426496201478</v>
       </c>
       <c r="R35" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2369,43 +2345,43 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>0.8942234848484848</v>
+        <v>0.925</v>
       </c>
       <c r="G36">
-        <v>0.04010840214088301</v>
+        <v>0.03016728621786092</v>
       </c>
       <c r="H36">
         <v>0.7777777777777778</v>
       </c>
       <c r="I36">
-        <v>0.07657804862272345</v>
+        <v>0.03513641844631534</v>
       </c>
       <c r="J36">
-        <v>0.7750582750582751</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K36">
-        <v>0.07930424467766627</v>
+        <v>0.03513641844631531</v>
       </c>
       <c r="L36">
-        <v>0.7810661457565482</v>
+        <v>0.8057671957671957</v>
       </c>
       <c r="M36">
-        <v>0.08135671397936681</v>
+        <v>0.04331267152170716</v>
       </c>
       <c r="N36">
-        <v>0.7750582750582751</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="O36">
-        <v>0.07930424467766627</v>
+        <v>0.03513641844631531</v>
       </c>
       <c r="P36">
-        <v>0.7669288851750292</v>
+        <v>0.7657457357457357</v>
       </c>
       <c r="Q36">
-        <v>0.08486346171989394</v>
+        <v>0.04140924068364827</v>
       </c>
       <c r="R36" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2413,43 +2389,43 @@
         <v>26</v>
       </c>
       <c r="F37">
-        <v>0.8942234848484848</v>
+        <v>0.925</v>
       </c>
       <c r="G37">
-        <v>0.04010840214088301</v>
+        <v>0.03016728621786092</v>
       </c>
       <c r="H37">
-        <v>0.7666666666666667</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="I37">
-        <v>0.07973722274670736</v>
+        <v>0.03513641844631534</v>
       </c>
       <c r="J37">
-        <v>0.763947163947164</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K37">
-        <v>0.08141001307571959</v>
+        <v>0.03513641844631531</v>
       </c>
       <c r="L37">
-        <v>0.7747307812013695</v>
+        <v>0.8057671957671957</v>
       </c>
       <c r="M37">
-        <v>0.08289051896528249</v>
+        <v>0.04331267152170716</v>
       </c>
       <c r="N37">
-        <v>0.763947163947164</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="O37">
-        <v>0.08141001307571959</v>
+        <v>0.03513641844631531</v>
       </c>
       <c r="P37">
-        <v>0.7533284555802457</v>
+        <v>0.7657457357457357</v>
       </c>
       <c r="Q37">
-        <v>0.08906972653872761</v>
+        <v>0.04140924068364827</v>
       </c>
       <c r="R37" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2457,43 +2433,43 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>0.8895987114737116</v>
+        <v>0.9199074074074074</v>
       </c>
       <c r="G38">
-        <v>0.03881514883206556</v>
+        <v>0.0224715946287252</v>
       </c>
       <c r="H38">
-        <v>0.7833333333333333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="I38">
-        <v>0.05931710140017394</v>
+        <v>0.05665577237325316</v>
       </c>
       <c r="J38">
-        <v>0.7815462315462315</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K38">
-        <v>0.0599032577580885</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="L38">
-        <v>0.8068609168609168</v>
+        <v>0.8324338624338624</v>
       </c>
       <c r="M38">
-        <v>0.06574860331568839</v>
+        <v>0.0658927957383834</v>
       </c>
       <c r="N38">
-        <v>0.7815462315462315</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O38">
-        <v>0.0599032577580885</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="P38">
-        <v>0.7735596918305565</v>
+        <v>0.8043171643171643</v>
       </c>
       <c r="Q38">
-        <v>0.06619927212723699</v>
+        <v>0.06090837325779238</v>
       </c>
       <c r="R38" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2501,43 +2477,43 @@
         <v>28</v>
       </c>
       <c r="F39">
-        <v>0.8895501489251491</v>
+        <v>0.9199074074074074</v>
       </c>
       <c r="G39">
-        <v>0.03847922480901986</v>
+        <v>0.0224715946287252</v>
       </c>
       <c r="H39">
-        <v>0.7666666666666667</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="I39">
-        <v>0.05152010275275393</v>
+        <v>0.05665577237325316</v>
       </c>
       <c r="J39">
-        <v>0.7643745143745144</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K39">
-        <v>0.05101366633080492</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="L39">
-        <v>0.7915103415103416</v>
+        <v>0.8324338624338624</v>
       </c>
       <c r="M39">
-        <v>0.06655045547197871</v>
+        <v>0.0658927957383834</v>
       </c>
       <c r="N39">
-        <v>0.7643745143745144</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O39">
-        <v>0.05101366633080492</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="P39">
-        <v>0.7555850309573449</v>
+        <v>0.8043171643171643</v>
       </c>
       <c r="Q39">
-        <v>0.05612862192371124</v>
+        <v>0.06090837325779238</v>
       </c>
       <c r="R39" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2545,43 +2521,43 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>0.8687645687645688</v>
+        <v>0.9106481481481481</v>
       </c>
       <c r="G40">
-        <v>0.03156901243293266</v>
+        <v>0.01385799032138494</v>
       </c>
       <c r="H40">
-        <v>0.7388888888888888</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="I40">
-        <v>0.0283278861866266</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="J40">
-        <v>0.7388111888111888</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K40">
-        <v>0.02719158597386248</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="L40">
-        <v>0.7402095072683308</v>
+        <v>0.8649999999999999</v>
       </c>
       <c r="M40">
-        <v>0.03098856736491978</v>
+        <v>0.03766322501484064</v>
       </c>
       <c r="N40">
-        <v>0.7388111888111888</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O40">
-        <v>0.02719158597386248</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="P40">
-        <v>0.7314361510098356</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="Q40">
-        <v>0.03193303676965128</v>
+        <v>0.03088515287607274</v>
       </c>
       <c r="R40" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2589,43 +2565,43 @@
         <v>30</v>
       </c>
       <c r="F41">
-        <v>0.8687645687645688</v>
+        <v>0.9106481481481481</v>
       </c>
       <c r="G41">
-        <v>0.03156901243293266</v>
+        <v>0.01385799032138494</v>
       </c>
       <c r="H41">
-        <v>0.7333333333333333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="I41">
-        <v>0.0283278861866266</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="J41">
-        <v>0.7332556332556333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K41">
-        <v>0.02979000104905061</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="L41">
-        <v>0.7338603009191245</v>
+        <v>0.8649999999999999</v>
       </c>
       <c r="M41">
-        <v>0.02965871507341749</v>
+        <v>0.03766322501484064</v>
       </c>
       <c r="N41">
-        <v>0.7332556332556333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O41">
-        <v>0.02979000104905061</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="P41">
-        <v>0.7267946808952198</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="Q41">
-        <v>0.03390198572312038</v>
+        <v>0.03088515287607274</v>
       </c>
       <c r="R41" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2633,43 +2609,43 @@
         <v>31</v>
       </c>
       <c r="F42">
-        <v>0.8359184796684798</v>
+        <v>0.8657407407407408</v>
       </c>
       <c r="G42">
-        <v>0.06546870521651087</v>
+        <v>0.0315359006776415</v>
       </c>
       <c r="H42">
-        <v>0.7777777777777778</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="I42">
-        <v>0.05826715823167507</v>
+        <v>0.05665577237325316</v>
       </c>
       <c r="J42">
-        <v>0.7754856254856255</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K42">
-        <v>0.05906808251914274</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="L42">
-        <v>0.7866733266733266</v>
+        <v>0.8324338624338624</v>
       </c>
       <c r="M42">
-        <v>0.05914350110532302</v>
+        <v>0.0658927957383834</v>
       </c>
       <c r="N42">
-        <v>0.7754856254856255</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O42">
-        <v>0.05906808251914274</v>
+        <v>0.05665577237325314</v>
       </c>
       <c r="P42">
-        <v>0.7669033996840683</v>
+        <v>0.8043171643171643</v>
       </c>
       <c r="Q42">
-        <v>0.06504139885246112</v>
+        <v>0.06090837325779238</v>
       </c>
       <c r="R42" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2677,43 +2653,43 @@
         <v>32</v>
       </c>
       <c r="F43">
-        <v>0.8317340067340068</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="G43">
-        <v>0.06137399912013244</v>
+        <v>0.01942238607722505</v>
       </c>
       <c r="H43">
         <v>0.7777777777777778</v>
       </c>
       <c r="I43">
-        <v>0.07657804862272345</v>
+        <v>0.03513641844631534</v>
       </c>
       <c r="J43">
-        <v>0.7750582750582751</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K43">
-        <v>0.07930424467766627</v>
+        <v>0.03513641844631531</v>
       </c>
       <c r="L43">
-        <v>0.7858029878618114</v>
+        <v>0.8057671957671957</v>
       </c>
       <c r="M43">
-        <v>0.07664325503603957</v>
+        <v>0.04331267152170716</v>
       </c>
       <c r="N43">
-        <v>0.7750582750582751</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="O43">
-        <v>0.07930424467766627</v>
+        <v>0.03513641844631531</v>
       </c>
       <c r="P43">
-        <v>0.7670105845214346</v>
+        <v>0.7657457357457357</v>
       </c>
       <c r="Q43">
-        <v>0.08476606455553969</v>
+        <v>0.04140924068364827</v>
       </c>
       <c r="R43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2721,43 +2697,43 @@
         <v>33</v>
       </c>
       <c r="F44">
-        <v>0.811957718207718</v>
+        <v>0.8435185185185186</v>
       </c>
       <c r="G44">
-        <v>0.02874275449039206</v>
+        <v>0.02256677334621098</v>
       </c>
       <c r="H44">
-        <v>0.7333333333333333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="I44">
-        <v>0.0283278861866266</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="J44">
-        <v>0.7332556332556333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="K44">
-        <v>0.02979000104905061</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="L44">
-        <v>0.7380652577556602</v>
+        <v>0.8649999999999999</v>
       </c>
       <c r="M44">
-        <v>0.02994975272643225</v>
+        <v>0.03766322501484064</v>
       </c>
       <c r="N44">
-        <v>0.7332556332556333</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O44">
-        <v>0.02979000104905061</v>
+        <v>0.02721655269759088</v>
       </c>
       <c r="P44">
-        <v>0.7270591056615421</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="Q44">
-        <v>0.03372432729462593</v>
+        <v>0.03088515287607274</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -2765,43 +2741,43 @@
         <v>34</v>
       </c>
       <c r="F45">
-        <v>0.8086538461538462</v>
+        <v>0.825</v>
       </c>
       <c r="G45">
-        <v>0.03769844553473965</v>
+        <v>0.04859126579037751</v>
       </c>
       <c r="H45">
-        <v>0.7444444444444445</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="I45">
-        <v>0.05091750772173158</v>
+        <v>0.06478835438717004</v>
       </c>
       <c r="J45">
-        <v>0.7448717948717949</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="K45">
-        <v>0.05026459404631948</v>
+        <v>0.06478835438717004</v>
       </c>
       <c r="L45">
-        <v>0.7586987522281641</v>
+        <v>0.7761111111111111</v>
       </c>
       <c r="M45">
-        <v>0.05399367355468065</v>
+        <v>0.06451184996253256</v>
       </c>
       <c r="N45">
-        <v>0.7448717948717949</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="O45">
-        <v>0.05026459404631948</v>
+        <v>0.06478835438717004</v>
       </c>
       <c r="P45">
-        <v>0.7432511449902754</v>
+        <v>0.7646575646575646</v>
       </c>
       <c r="Q45">
-        <v>0.04896200197917</v>
+        <v>0.06617466686175826</v>
       </c>
       <c r="R45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -2809,43 +2785,43 @@
         <v>35</v>
       </c>
       <c r="F46">
-        <v>0.7571386946386947</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="G46">
-        <v>0.01626098646886655</v>
+        <v>0.07728015412913089</v>
       </c>
       <c r="H46">
-        <v>0.6777777777777778</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="I46">
-        <v>0.02222222222222223</v>
+        <v>0.1030402055055078</v>
       </c>
       <c r="J46">
-        <v>0.6761849261849263</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K46">
-        <v>0.02168131529182204</v>
+        <v>0.1030402055055079</v>
       </c>
       <c r="L46">
-        <v>0.6769202692732104</v>
+        <v>0.7622222222222221</v>
       </c>
       <c r="M46">
-        <v>0.02437665272336069</v>
+        <v>0.1021334525338306</v>
       </c>
       <c r="N46">
-        <v>0.6761849261849263</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="O46">
-        <v>0.02168131529182204</v>
+        <v>0.1030402055055079</v>
       </c>
       <c r="P46">
-        <v>0.6684598277963598</v>
+        <v>0.7567210567210567</v>
       </c>
       <c r="Q46">
-        <v>0.02538733597971047</v>
+        <v>0.1016685252727103</v>
       </c>
       <c r="R46" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -2853,43 +2829,43 @@
         <v>36</v>
       </c>
       <c r="F47">
-        <v>0.7571386946386947</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="G47">
-        <v>0.01626098646886655</v>
+        <v>0.07728015412913089</v>
       </c>
       <c r="H47">
-        <v>0.6777777777777778</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="I47">
-        <v>0.02222222222222223</v>
+        <v>0.1030402055055078</v>
       </c>
       <c r="J47">
-        <v>0.6761849261849263</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K47">
-        <v>0.02168131529182204</v>
+        <v>0.1030402055055079</v>
       </c>
       <c r="L47">
-        <v>0.6769202692732104</v>
+        <v>0.7622222222222221</v>
       </c>
       <c r="M47">
-        <v>0.02437665272336069</v>
+        <v>0.1021334525338306</v>
       </c>
       <c r="N47">
-        <v>0.6761849261849263</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="O47">
-        <v>0.02168131529182204</v>
+        <v>0.1030402055055079</v>
       </c>
       <c r="P47">
-        <v>0.6684598277963598</v>
+        <v>0.7567210567210567</v>
       </c>
       <c r="Q47">
-        <v>0.02538733597971047</v>
+        <v>0.1016685252727103</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -2897,43 +2873,43 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>0.7447358197358197</v>
+        <v>0.8157407407407409</v>
       </c>
       <c r="G48">
-        <v>0.02348398888388991</v>
+        <v>0.06993039847592301</v>
       </c>
       <c r="H48">
-        <v>0.6777777777777778</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="I48">
-        <v>0.02222222222222223</v>
+        <v>0.1030402055055078</v>
       </c>
       <c r="J48">
-        <v>0.6761849261849263</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="K48">
-        <v>0.02168131529182204</v>
+        <v>0.1030402055055079</v>
       </c>
       <c r="L48">
-        <v>0.6769202692732104</v>
+        <v>0.7622222222222221</v>
       </c>
       <c r="M48">
-        <v>0.02437665272336069</v>
+        <v>0.1021334525338306</v>
       </c>
       <c r="N48">
-        <v>0.6761849261849263</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="O48">
-        <v>0.02168131529182204</v>
+        <v>0.1030402055055079</v>
       </c>
       <c r="P48">
-        <v>0.6684598277963598</v>
+        <v>0.7567210567210567</v>
       </c>
       <c r="Q48">
-        <v>0.02538733597971047</v>
+        <v>0.1016685252727103</v>
       </c>
       <c r="R48" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
